--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.74</v>
+        <v>1.4</v>
       </c>
       <c r="O32">
-        <v>3.86</v>
+        <v>5.2</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>9.35</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>4.74</v>
       </c>
       <c r="O33">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="P33">
-        <v>9.35</v>
+        <v>1.83</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G8">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G18">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G21">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G37">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.4</v>
+        <v>4.74</v>
       </c>
       <c r="O32">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="P32">
-        <v>9.35</v>
+        <v>1.83</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.74</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
-        <v>3.86</v>
+        <v>5.2</v>
       </c>
       <c r="P33">
-        <v>1.83</v>
+        <v>9.35</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N35">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G41">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.57</v>
+        <v>2.75</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="O18">
         <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>3.07</v>
+        <v>3.27</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="Q21">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.92</v>
+        <v>2.43</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="O17">
         <v>3.3</v>
       </c>
       <c r="P17">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.07</v>
+        <v>3.27</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.57</v>
+        <v>2.28</v>
       </c>
       <c r="Q21">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="O16">
         <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>3.07</v>
+        <v>3.57</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.11</v>
+        <v>2.92</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>3.57</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>2.28</v>
+        <v>3.07</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O28">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P28">
-        <v>3.33</v>
+        <v>4.82</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>4.82</v>
+        <v>3.33</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>6.65</v>
+        <v>3.64</v>
       </c>
       <c r="P7">
-        <v>11.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>1.14</v>
       </c>
       <c r="O8">
-        <v>3.64</v>
+        <v>6.65</v>
       </c>
       <c r="P8">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="Q8">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU42"/>
+  <dimension ref="A1:AU43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:00:00</t>
+          <t>2026-10-27 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-27 13:00:00</t>
+          <t>2026-10-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="O8">
-        <v>6.65</v>
+        <v>3.64</v>
       </c>
       <c r="P8">
-        <v>11.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-27 14:00:00</t>
+          <t>2026-10-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:00</t>
+          <t>2026-10-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.96</v>
+        <v>4.61</v>
       </c>
       <c r="O11">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P11">
-        <v>2.53</v>
+        <v>1.78</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00:00</t>
+          <t>2026-10-27 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.17</v>
+        <v>2.13</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P15">
-        <v>2.11</v>
+        <v>3.15</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.29</v>
+        <v>3.17</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>3.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-27 16:00:00</t>
+          <t>2026-10-27 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.57</v>
+        <v>3.27</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.28</v>
+        <v>3.57</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,68 +3891,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.33</v>
+        <v>2.92</v>
       </c>
       <c r="O22">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>6.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-27 16:45:00</t>
+          <t>2026-10-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G23">
@@ -4054,68 +4054,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="O23">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="P23">
-        <v>2.45</v>
+        <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>3.93</v>
+        <v>4.6</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="R26">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U26">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="V26">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
       <c r="AD26">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK26">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,68 +4706,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27">
-        <v>3.09</v>
+        <v>1.77</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P27">
-        <v>2.07</v>
+        <v>3.93</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.59</v>
+        <v>3.09</v>
       </c>
       <c r="O28">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.82</v>
+        <v>2.07</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,17 +5032,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P29">
-        <v>3.33</v>
+        <v>4.82</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>4.74</v>
       </c>
       <c r="O33">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="P33">
-        <v>9.35</v>
+        <v>1.83</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.07</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
-        <v>3.22</v>
+        <v>5.2</v>
       </c>
       <c r="P34">
-        <v>3.51</v>
+        <v>9.35</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-27 20:00:00</t>
+          <t>2026-10-27 16:45:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G35">
@@ -6010,17 +6010,17 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-27 21:00:00</t>
+          <t>2026-10-27 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,141 +7123,304 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Progrès Sakiet Eddaïer</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stade Tunisien</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>ES Tunis</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Hammam-Sousse</t>
         </is>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
-      <c r="AD42">
-        <v>0</v>
-      </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
-      <c r="AF42">
-        <v>0</v>
-      </c>
-      <c r="AG42">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
-      <c r="AK42">
-        <v>0</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>2026-10-27 21:00:00</t>
         </is>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.28</v>
+        <v>3.07</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1296,55 +1296,55 @@
         <v>4.75</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,55 +1459,55 @@
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>1.78</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.53</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>1.83</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>9.35</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>3.51</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA35">
         <v>2</v>
@@ -6059,19 +6059,19 @@
         <v>1.79</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.1</v>
+        <v>1.14</v>
       </c>
       <c r="O8">
-        <v>3.64</v>
+        <v>6.65</v>
       </c>
       <c r="P8">
-        <v>2.82</v>
+        <v>11.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>2.1</v>
+      </c>
+      <c r="O9">
+        <v>3.64</v>
+      </c>
+      <c r="P9">
+        <v>2.82</v>
+      </c>
+      <c r="Q9">
+        <v>2.6</v>
+      </c>
+      <c r="R9">
+        <v>2.4</v>
+      </c>
+      <c r="S9">
+        <v>1.22</v>
+      </c>
+      <c r="T9">
+        <v>3.75</v>
+      </c>
+      <c r="U9">
+        <v>2.2</v>
+      </c>
+      <c r="V9">
+        <v>1.62</v>
+      </c>
+      <c r="W9">
         <v>1.14</v>
       </c>
-      <c r="O9">
-        <v>6.65</v>
-      </c>
-      <c r="P9">
-        <v>11.5</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>3.15</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.74</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
-        <v>3.86</v>
+        <v>5.2</v>
       </c>
       <c r="P33">
+        <v>9.35</v>
+      </c>
+      <c r="Q33">
         <v>1.83</v>
       </c>
-      <c r="Q33">
-        <v>4.95</v>
-      </c>
       <c r="R33">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AB33">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AC33">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD33">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.17</v>
+        <v>3.24</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.4</v>
+        <v>4.74</v>
       </c>
       <c r="O34">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="P34">
-        <v>9.35</v>
+        <v>1.83</v>
       </c>
       <c r="Q34">
-        <v>1.83</v>
+        <v>4.95</v>
       </c>
       <c r="R34">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AA34">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AB34">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AC34">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE34">
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>3.24</v>
+        <v>1.17</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -4230,34 +4230,34 @@
         <v>2.45</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA24">
         <v>2.1</v>
@@ -4266,19 +4266,19 @@
         <v>1.7</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>2.84</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.21</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q32">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="Q3">
         <v>2.75</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S6">
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U6">
         <v>3.07</v>
@@ -1462,19 +1462,19 @@
         <v>3.4</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
         <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
         <v>1.11</v>
@@ -1498,7 +1498,7 @@
         <v>2.81</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
@@ -1507,7 +1507,7 @@
         <v>1.61</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK7">
         <v>1.33</v>
@@ -1616,10 +1616,10 @@
         <v>1.14</v>
       </c>
       <c r="O8">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="P8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Q8">
         <v>1.44</v>
@@ -1652,10 +1652,10 @@
         <v>6.9</v>
       </c>
       <c r="AA8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB8">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC8">
         <v>1.67</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="O9">
         <v>3.64</v>
       </c>
       <c r="P9">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="Q9">
         <v>2.6</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1296,34 +1296,34 @@
         <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="R6">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="U6">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="AA6">
         <v>2.1</v>
@@ -1332,10 +1332,10 @@
         <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.04</v>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.61</v>
+        <v>4.4</v>
       </c>
       <c r="O11">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>5.49</v>
+        <v>5.79</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2123,10 +2123,10 @@
         <v>2.62</v>
       </c>
       <c r="U11">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2135,31 +2135,31 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z11">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA11">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AB11">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="O12">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
         <v>1.33</v>
@@ -2310,7 +2310,7 @@
         <v>2.08</v>
       </c>
       <c r="AC12">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="AD12">
         <v>1.43</v>
@@ -2319,10 +2319,10 @@
         <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O33">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>9.35</v>
+        <v>8.5</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -5733,7 +5733,7 @@
         <v>2.16</v>
       </c>
       <c r="AC33">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AD33">
         <v>1.44</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK33">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.74</v>
+        <v>4.2</v>
       </c>
       <c r="O34">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q34">
         <v>4.95</v>
@@ -5902,7 +5902,7 @@
         <v>1.43</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.73</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1622,25 +1622,25 @@
         <v>11</v>
       </c>
       <c r="Q8">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="R8">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="S8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U8">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V8">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="W8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1785,7 +1785,7 @@
         <v>2.83</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
         <v>2.4</v>
@@ -1812,28 +1812,28 @@
         <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA9">
         <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC9">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AD9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG9">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1951,13 +1951,13 @@
         <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
         <v>2.45</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q14">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="R14">
         <v>2.15</v>
@@ -2609,16 +2609,16 @@
         <v>1.35</v>
       </c>
       <c r="T14">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
         <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2630,13 +2630,13 @@
         <v>3.68</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC14">
-        <v>2.83</v>
+        <v>3.16</v>
       </c>
       <c r="AD14">
         <v>1.33</v>
@@ -2664,7 +2664,7 @@
         <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q15">
         <v>2.43</v>
@@ -2772,10 +2772,10 @@
         <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
         <v>1.5</v>
@@ -2787,13 +2787,13 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.94</v>
+        <v>4.23</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
         <v>2.11</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.73</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.25</v>
       </c>
       <c r="P19">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="O20">
         <v>3.4</v>
@@ -3901,7 +3901,7 @@
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W23">
         <v>1.14</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="Q24">
         <v>3.44</v>
       </c>
       <c r="R24">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>1.38</v>
@@ -4242,10 +4242,10 @@
         <v>2.65</v>
       </c>
       <c r="U24">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
         <v>1.04</v>
@@ -4260,10 +4260,10 @@
         <v>2.83</v>
       </c>
       <c r="AA24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC24">
         <v>3.76</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R25">
         <v>2.28</v>
@@ -4441,7 +4441,7 @@
         <v>1.48</v>
       </c>
       <c r="AG25">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK25">
         <v>1.57</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O26">
         <v>4</v>
       </c>
       <c r="P26">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q26">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="U26">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="AA26">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O27">
         <v>3.9</v>
@@ -5202,10 +5202,10 @@
         <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="P30">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="Q30">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1290,7 +1290,7 @@
         <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
         <v>4.2</v>
@@ -1785,7 +1785,7 @@
         <v>2.83</v>
       </c>
       <c r="Q9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
         <v>2.4</v>
@@ -1812,13 +1812,13 @@
         <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA9">
         <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC9">
         <v>2.22</v>
@@ -1830,10 +1830,10 @@
         <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG9">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>1.35</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U14">
         <v>2.44</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q15">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2790,7 +2790,7 @@
         <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="AA15">
         <v>1.68</v>
@@ -2808,10 +2808,10 @@
         <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
         <v>1.73</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
         <v>4.95</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="R35">
         <v>1.97</v>
@@ -6032,7 +6032,7 @@
         <v>1.43</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U35">
         <v>2.96</v>
@@ -6053,10 +6053,10 @@
         <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB35">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC35">
         <v>3.5</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
         <v>1.68</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2319,10 +2319,10 @@
         <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>1.83</v>
@@ -5857,13 +5857,13 @@
         <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q34">
-        <v>4.95</v>
+        <v>4.24</v>
       </c>
       <c r="R34">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S34">
         <v>1.3</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU43"/>
+  <dimension ref="A1:AU45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00:00</t>
+          <t>2026-10-27 05:30:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3">
@@ -794,68 +794,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:40:00</t>
+          <t>2026-10-27 09:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G4">
@@ -957,68 +957,68 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-27 10:30:00</t>
+          <t>2026-10-27 09:40:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-27 11:00:00</t>
+          <t>2026-10-27 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-27 12:00:00</t>
+          <t>2026-10-27 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q7">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="U7">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="V7">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
+        <v>1.36</v>
+      </c>
+      <c r="Z7">
+        <v>3.02</v>
+      </c>
+      <c r="AA7">
+        <v>2.1</v>
+      </c>
+      <c r="AB7">
+        <v>1.65</v>
+      </c>
+      <c r="AC7">
+        <v>3.75</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.04</v>
+      </c>
+      <c r="AF7">
+        <v>1.97</v>
+      </c>
+      <c r="AG7">
+        <v>1.73</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.22</v>
       </c>
-      <c r="Z7">
-        <v>3.8</v>
-      </c>
-      <c r="AA7">
-        <v>1.75</v>
-      </c>
-      <c r="AB7">
-        <v>1.93</v>
-      </c>
-      <c r="AC7">
-        <v>2.81</v>
-      </c>
-      <c r="AD7">
-        <v>1.33</v>
-      </c>
-      <c r="AE7">
-        <v>1.1</v>
-      </c>
-      <c r="AF7">
-        <v>1.61</v>
-      </c>
-      <c r="AG7">
-        <v>2.2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.6</v>
-      </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>2.09</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-27 13:00:00</t>
+          <t>2026-10-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.14</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="R8">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
-        <v>1.88</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC8">
-        <v>1.67</v>
+        <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>2.04</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AK8">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.09</v>
+        <v>1.18</v>
       </c>
       <c r="O9">
-        <v>3.64</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>2.83</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>1.52</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z9">
-        <v>4.95</v>
+        <v>6.9</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="AC9">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="AE9">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AF9">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AK9">
-        <v>1.53</v>
+        <v>5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.59</v>
+        <v>2.09</v>
       </c>
       <c r="O10">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="P10">
-        <v>4.77</v>
+        <v>2.83</v>
       </c>
       <c r="Q10">
+        <v>2.8</v>
+      </c>
+      <c r="R10">
+        <v>2.4</v>
+      </c>
+      <c r="S10">
+        <v>1.22</v>
+      </c>
+      <c r="T10">
+        <v>3.75</v>
+      </c>
+      <c r="U10">
         <v>2.2</v>
       </c>
-      <c r="R10">
-        <v>2.39</v>
-      </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.3</v>
-      </c>
-      <c r="U10">
-        <v>2.45</v>
-      </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="AA10">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AB10">
-        <v>2.09</v>
+        <v>2.41</v>
       </c>
       <c r="AC10">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-27 14:00:00</t>
+          <t>2026-10-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.4</v>
+        <v>1.59</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>4.77</v>
       </c>
       <c r="Q11">
-        <v>5.79</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
+        <v>3.3</v>
+      </c>
+      <c r="U11">
+        <v>2.45</v>
+      </c>
+      <c r="V11">
+        <v>1.47</v>
+      </c>
+      <c r="W11">
+        <v>1.12</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.68</v>
+      </c>
+      <c r="AB11">
+        <v>2.09</v>
+      </c>
+      <c r="AC11">
         <v>2.62</v>
       </c>
-      <c r="U11">
-        <v>3.23</v>
-      </c>
-      <c r="V11">
-        <v>1.32</v>
-      </c>
-      <c r="W11">
-        <v>1.07</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.34</v>
-      </c>
-      <c r="Z11">
-        <v>2.78</v>
-      </c>
-      <c r="AA11">
-        <v>2.17</v>
-      </c>
-      <c r="AB11">
+      <c r="AD11">
+        <v>1.38</v>
+      </c>
+      <c r="AE11">
+        <v>1.15</v>
+      </c>
+      <c r="AF11">
         <v>1.67</v>
       </c>
-      <c r="AC11">
-        <v>3.9</v>
-      </c>
-      <c r="AD11">
-        <v>1.23</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>2</v>
-      </c>
       <c r="AG11">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:00</t>
+          <t>2026-10-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30:00</t>
+          <t>2026-10-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00:00</t>
+          <t>2026-10-27 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q14">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U14">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="AA14">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AC14">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00:00</t>
+          <t>2026-10-27 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.06</v>
+        <v>2.43</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="P16">
+        <v>2.37</v>
+      </c>
+      <c r="Q16">
+        <v>3.12</v>
+      </c>
+      <c r="R16">
         <v>2.15</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="O17">
+        <v>3.6</v>
+      </c>
+      <c r="P17">
+        <v>3.2</v>
+      </c>
+      <c r="Q17">
+        <v>2.55</v>
+      </c>
+      <c r="R17">
+        <v>2.24</v>
+      </c>
+      <c r="S17">
+        <v>1.28</v>
+      </c>
+      <c r="T17">
         <v>3.3</v>
       </c>
-      <c r="P17">
-        <v>3.01</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-27 16:00:00</t>
+          <t>2026-10-27 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.11</v>
+        <v>3.06</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>3.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-27 16:00:00</t>
+          <t>2026-10-27 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.56</v>
+        <v>3.01</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.91</v>
+        <v>2.11</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.28</v>
+        <v>3.26</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>2.75</v>
+        <v>3.56</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G23">
@@ -4054,68 +4054,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="O23">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-27 16:45:00</t>
+          <t>2026-10-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>2.39</v>
+        <v>3.06</v>
       </c>
       <c r="Q24">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-27 16:45:00</t>
+          <t>2026-10-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,84 +4380,84 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="O25">
+        <v>4.8</v>
+      </c>
+      <c r="P25">
+        <v>6.5</v>
+      </c>
+      <c r="Q25">
+        <v>1.75</v>
+      </c>
+      <c r="R25">
+        <v>2.6</v>
+      </c>
+      <c r="S25">
+        <v>1.25</v>
+      </c>
+      <c r="T25">
+        <v>3.5</v>
+      </c>
+      <c r="U25">
+        <v>2.24</v>
+      </c>
+      <c r="V25">
+        <v>1.57</v>
+      </c>
+      <c r="W25">
+        <v>1.14</v>
+      </c>
+      <c r="X25">
+        <v>1.03</v>
+      </c>
+      <c r="Y25">
+        <v>1.1</v>
+      </c>
+      <c r="Z25">
         <v>3.4</v>
       </c>
-      <c r="P25">
-        <v>3</v>
-      </c>
-      <c r="Q25">
-        <v>2.76</v>
-      </c>
-      <c r="R25">
+      <c r="AA25">
+        <v>1.53</v>
+      </c>
+      <c r="AB25">
         <v>2.28</v>
-      </c>
-      <c r="S25">
-        <v>1.24</v>
-      </c>
-      <c r="T25">
-        <v>3.55</v>
-      </c>
-      <c r="U25">
-        <v>2.23</v>
-      </c>
-      <c r="V25">
-        <v>1.56</v>
-      </c>
-      <c r="W25">
-        <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.13</v>
-      </c>
-      <c r="Z25">
-        <v>4.55</v>
-      </c>
-      <c r="AA25">
-        <v>1.57</v>
-      </c>
-      <c r="AB25">
-        <v>2.29</v>
       </c>
       <c r="AC25">
         <v>2.38</v>
       </c>
       <c r="AD25">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
+        <v>1.22</v>
+      </c>
+      <c r="AF25">
+        <v>1.75</v>
+      </c>
+      <c r="AG25">
+        <v>1.95</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.15</v>
       </c>
-      <c r="AF25">
-        <v>1.48</v>
-      </c>
-      <c r="AG25">
-        <v>2.47</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.39</v>
-      </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="Q26">
-        <v>2.25</v>
+        <v>3.44</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>3.32</v>
+        <v>2.65</v>
       </c>
       <c r="U26">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="V26">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>4.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA26">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>1.64</v>
       </c>
       <c r="AC26">
-        <v>2.52</v>
+        <v>3.76</v>
       </c>
       <c r="AD26">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.93</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U27">
         <v>2.23</v>
@@ -4737,37 +4737,37 @@
         <v>1.56</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB27">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AC27">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE27">
         <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK27">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.09</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>2.07</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>4.82</v>
+        <v>3.93</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>3.09</v>
       </c>
       <c r="O30">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.53</v>
+        <v>2.07</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.2</v>
+        <v>1.81</v>
       </c>
       <c r="O34">
         <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>1.36</v>
+      </c>
+      <c r="O35">
+        <v>5</v>
+      </c>
+      <c r="P35">
+        <v>9</v>
+      </c>
+      <c r="Q35">
+        <v>1.83</v>
+      </c>
+      <c r="R35">
+        <v>2.43</v>
+      </c>
+      <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.14</v>
+      </c>
+      <c r="U35">
+        <v>2.51</v>
+      </c>
+      <c r="V35">
+        <v>1.49</v>
+      </c>
+      <c r="W35">
+        <v>1.08</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>1.19</v>
+      </c>
+      <c r="Z35">
+        <v>4</v>
+      </c>
+      <c r="AA35">
+        <v>1.71</v>
+      </c>
+      <c r="AB35">
+        <v>2.16</v>
+      </c>
+      <c r="AC35">
+        <v>2.77</v>
+      </c>
+      <c r="AD35">
+        <v>1.44</v>
+      </c>
+      <c r="AE35">
+        <v>1.16</v>
+      </c>
+      <c r="AF35">
         <v>2</v>
       </c>
-      <c r="O35">
-        <v>3.2</v>
-      </c>
-      <c r="P35">
-        <v>3.3</v>
-      </c>
-      <c r="Q35">
-        <v>2.69</v>
-      </c>
-      <c r="R35">
-        <v>1.97</v>
-      </c>
-      <c r="S35">
-        <v>1.43</v>
-      </c>
-      <c r="T35">
-        <v>2.57</v>
-      </c>
-      <c r="U35">
-        <v>2.96</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.04</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.36</v>
-      </c>
-      <c r="Z35">
-        <v>2.88</v>
-      </c>
-      <c r="AA35">
-        <v>2.1</v>
-      </c>
-      <c r="AB35">
-        <v>1.7</v>
-      </c>
-      <c r="AC35">
-        <v>3.5</v>
-      </c>
-      <c r="AD35">
-        <v>1.22</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
-      <c r="AF35">
-        <v>1.85</v>
-      </c>
       <c r="AG35">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>1.68</v>
+        <v>2.98</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-27 20:00:00</t>
+          <t>2026-10-27 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-27 21:00:00</t>
+          <t>2026-10-27 16:45:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-27 21:00:00</t>
+          <t>2026-10-27 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,141 +7286,467 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Etoile du Sahel</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Club Africain</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Progrès Sakiet Eddaïer</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stade Tunisien</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>ES Tunis</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Hammam-Sousse</t>
         </is>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>-1</v>
-      </c>
-      <c r="AN43">
-        <v>-1</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>-1</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>2026-10-27 21:00:00</t>
         </is>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1495,10 +1495,10 @@
         <v>1.65</v>
       </c>
       <c r="AC7">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE7">
         <v>1.04</v>
@@ -1652,7 +1652,7 @@
         <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
         <v>1.93</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="O9">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q9">
         <v>1.52</v>
@@ -1818,7 +1818,7 @@
         <v>1.28</v>
       </c>
       <c r="AB9">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC9">
         <v>1.67</v>
@@ -1960,28 +1960,28 @@
         <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z10">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC10">
         <v>2.17</v>
@@ -1993,10 +1993,10 @@
         <v>1.21</v>
       </c>
       <c r="AF10">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG10">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.44</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q16">
         <v>3.12</v>
@@ -2953,7 +2953,7 @@
         <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
         <v>1.74</v>
@@ -2962,13 +2962,13 @@
         <v>1.94</v>
       </c>
       <c r="AC16">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O17">
         <v>3.6</v>
@@ -4553,7 +4553,7 @@
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
         <v>3.44</v>
@@ -4719,7 +4719,7 @@
         <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
         <v>2.28</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AK27">
         <v>1.57</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
         <v>4</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
         <v>2.22</v>
@@ -653,16 +653,16 @@
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.04</v>
@@ -1984,13 +1984,13 @@
         <v>2.46</v>
       </c>
       <c r="AC10">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD10">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AE10">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
         <v>1.39</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O14">
         <v>3.4</v>
@@ -5371,55 +5371,55 @@
         <v>4.82</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X31">
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>3.8</v>
       </c>
       <c r="P36">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
         <v>4.24</v>
@@ -6195,13 +6195,13 @@
         <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -6216,25 +6216,25 @@
         <v>3.78</v>
       </c>
       <c r="AA36">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC36">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE36">
         <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="O4">
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1453,7 +1453,7 @@
         <v>1.67</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
         <v>4.2</v>
@@ -1652,7 +1652,7 @@
         <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
         <v>1.93</v>
@@ -1686,7 +1686,7 @@
         <v>1.6</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>2.4</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U10">
         <v>2.1</v>
@@ -2132,7 +2132,7 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="O14">
         <v>3.4</v>
       </c>
       <c r="P14">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
         <v>3.09</v>
@@ -2609,7 +2609,7 @@
         <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="U14">
         <v>2.5</v>
@@ -2618,37 +2618,37 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC14">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="AD14">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
         <v>1.73</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="O20">
+        <v>3.5</v>
+      </c>
+      <c r="P20">
         <v>3.4</v>
       </c>
-      <c r="P20">
-        <v>3.26</v>
-      </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P22">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.43</v>
+        <v>3.26</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4556,16 +4556,16 @@
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="R26">
         <v>2</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U26">
         <v>3.2</v>
@@ -4574,37 +4574,37 @@
         <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA26">
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC26">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AD26">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="O27">
         <v>3.4</v>
@@ -4719,55 +4719,55 @@
         <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="U27">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="V27">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AD27">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AG27">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.15</v>
@@ -4912,7 +4912,7 @@
         <v>4.3</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB28">
         <v>2.19</v>
@@ -5208,55 +5208,55 @@
         <v>2.07</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="P31">
-        <v>4.82</v>
+        <v>3.53</v>
       </c>
       <c r="Q31">
-        <v>1.82</v>
+        <v>2.56</v>
       </c>
       <c r="R31">
-        <v>2.65</v>
+        <v>2.29</v>
       </c>
       <c r="S31">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
+        <v>1.16</v>
+      </c>
+      <c r="Z31">
+        <v>4.15</v>
+      </c>
+      <c r="AA31">
+        <v>1.62</v>
+      </c>
+      <c r="AB31">
+        <v>2.21</v>
+      </c>
+      <c r="AC31">
+        <v>2.43</v>
+      </c>
+      <c r="AD31">
+        <v>1.44</v>
+      </c>
+      <c r="AE31">
         <v>1.15</v>
       </c>
-      <c r="Z31">
-        <v>5.1</v>
-      </c>
-      <c r="AA31">
-        <v>1.45</v>
-      </c>
-      <c r="AB31">
-        <v>2.43</v>
-      </c>
-      <c r="AC31">
-        <v>2.15</v>
-      </c>
-      <c r="AD31">
-        <v>1.6</v>
-      </c>
-      <c r="AE31">
-        <v>1.24</v>
-      </c>
       <c r="AF31">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O32">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="P32">
-        <v>3.53</v>
+        <v>4.82</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="Q35">
         <v>1.83</v>
@@ -6053,16 +6053,16 @@
         <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB35">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AC35">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
         <v>1.16</v>
@@ -6195,13 +6195,13 @@
         <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -6210,10 +6210,10 @@
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="AA36">
         <v>1.68</v>
@@ -6228,7 +6228,7 @@
         <v>1.48</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
         <v>1.67</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1492,7 +1492,7 @@
         <v>2.1</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
         <v>3.58</v>
@@ -1661,7 +1661,7 @@
         <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
@@ -1815,7 +1815,7 @@
         <v>6.9</v>
       </c>
       <c r="AA9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB9">
         <v>3.28</v>
@@ -1948,7 +1948,7 @@
         <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
         <v>2.4</v>
@@ -1957,10 +1957,10 @@
         <v>1.2</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
         <v>1.67</v>
@@ -1972,31 +1972,31 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z10">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA10">
         <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC10">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF10">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AG10">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,22 +2923,22 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q16">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2947,28 +2947,28 @@
         <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
@@ -3095,7 +3095,7 @@
         <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
         <v>3.3</v>
@@ -3104,7 +3104,7 @@
         <v>2.32</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3113,13 +3113,13 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>4.21</v>
+        <v>3.92</v>
       </c>
       <c r="AA17">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
         <v>2.11</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
         <v>1.73</v>
@@ -3246,7 +3246,7 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P18">
         <v>2.18</v>
@@ -3258,7 +3258,7 @@
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
         <v>3.32</v>
@@ -3270,7 +3270,7 @@
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -3415,55 +3415,55 @@
         <v>2.9</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,19 +3575,19 @@
         <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
         <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U20">
         <v>2.63</v>
@@ -3599,7 +3599,7 @@
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.21</v>
@@ -3620,7 +3620,7 @@
         <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.66</v>
@@ -3789,7 +3789,7 @@
         <v>1.84</v>
       </c>
       <c r="AG21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U23">
         <v>2.45</v>
@@ -4131,7 +4131,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.24</v>
@@ -4266,7 +4266,7 @@
         <v>1.84</v>
       </c>
       <c r="AC24">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD24">
         <v>1.31</v>
@@ -4556,16 +4556,16 @@
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R26">
         <v>2</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U26">
         <v>3.2</v>
@@ -4574,37 +4574,37 @@
         <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA26">
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC26">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD26">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AG26">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB27">
         <v>2.43</v>
@@ -4761,7 +4761,7 @@
         <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
@@ -4882,55 +4882,55 @@
         <v>4.8</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U28">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AB28">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AC28">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD28">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>2.07</v>
       </c>
       <c r="Q30">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="R30">
         <v>2.25</v>
@@ -5217,7 +5217,7 @@
         <v>1.26</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
         <v>2.32</v>
@@ -5226,19 +5226,19 @@
         <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
@@ -5247,13 +5247,13 @@
         <v>2.56</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
         <v>2.3</v>
@@ -5371,55 +5371,55 @@
         <v>3.53</v>
       </c>
       <c r="Q31">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
+        <v>2.3</v>
+      </c>
+      <c r="S31">
+        <v>1.27</v>
+      </c>
+      <c r="T31">
+        <v>3.6</v>
+      </c>
+      <c r="U31">
         <v>2.29</v>
       </c>
-      <c r="S31">
-        <v>1.26</v>
-      </c>
-      <c r="T31">
-        <v>3.4</v>
-      </c>
-      <c r="U31">
-        <v>2.26</v>
-      </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>4.44</v>
       </c>
       <c r="AA31">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         <v>4.82</v>
       </c>
       <c r="Q32">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R32">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U32">
         <v>2.14</v>
@@ -5564,10 +5564,10 @@
         <v>4.7</v>
       </c>
       <c r="AA32">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AB32">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AC32">
         <v>2.33</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
+        <v>3.45</v>
+      </c>
+      <c r="P2">
+        <v>2.14</v>
+      </c>
+      <c r="Q2">
+        <v>3.48</v>
+      </c>
+      <c r="R2">
+        <v>2.12</v>
+      </c>
+      <c r="S2">
+        <v>1.29</v>
+      </c>
+      <c r="T2">
         <v>3.4</v>
       </c>
-      <c r="P2">
-        <v>2.22</v>
-      </c>
-      <c r="Q2">
-        <v>3.52</v>
-      </c>
-      <c r="R2">
-        <v>2.05</v>
-      </c>
-      <c r="S2">
-        <v>1.3</v>
-      </c>
-      <c r="T2">
-        <v>3.3</v>
-      </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W2">
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>3.94</v>
+        <v>4.45</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AB2">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD2">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1954,16 +1954,16 @@
         <v>2.4</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T10">
         <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W10">
         <v>1.17</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.5</v>
@@ -2618,7 +2618,7 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
         <v>3.7</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q15">
         <v>2.3</v>
       </c>
       <c r="R15">
+        <v>2.3</v>
+      </c>
+      <c r="S15">
+        <v>1.29</v>
+      </c>
+      <c r="T15">
+        <v>3.3</v>
+      </c>
+      <c r="U15">
         <v>2.29</v>
       </c>
-      <c r="S15">
-        <v>1.26</v>
-      </c>
-      <c r="T15">
-        <v>3.25</v>
-      </c>
-      <c r="U15">
-        <v>2.32</v>
-      </c>
       <c r="V15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC15">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
@@ -2932,7 +2932,7 @@
         <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
         <v>2.95</v>
@@ -2956,7 +2956,7 @@
         <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
         <v>1.87</v>
@@ -3095,7 +3095,7 @@
         <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
         <v>3.3</v>
@@ -3246,7 +3246,7 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
         <v>2.18</v>
@@ -3261,7 +3261,7 @@
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
         <v>2.55</v>
@@ -3270,7 +3270,7 @@
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3300,7 +3300,7 @@
         <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.63</v>
@@ -3436,34 +3436,34 @@
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC19">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
         <v>3.5</v>
       </c>
       <c r="Q20">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U20">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.3</v>
+      </c>
+      <c r="Z20">
+        <v>2.97</v>
+      </c>
+      <c r="AA20">
+        <v>2.06</v>
+      </c>
+      <c r="AB20">
+        <v>1.71</v>
+      </c>
+      <c r="AC20">
+        <v>3.58</v>
+      </c>
+      <c r="AD20">
+        <v>1.21</v>
+      </c>
+      <c r="AE20">
         <v>1.03</v>
       </c>
-      <c r="Y20">
-        <v>1.21</v>
-      </c>
-      <c r="Z20">
-        <v>3.58</v>
-      </c>
-      <c r="AA20">
-        <v>1.8</v>
-      </c>
-      <c r="AB20">
-        <v>1.94</v>
-      </c>
-      <c r="AC20">
-        <v>2.92</v>
-      </c>
-      <c r="AD20">
-        <v>1.31</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
       <c r="AF20">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG20">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P21">
-        <v>3.76</v>
+        <v>2.98</v>
       </c>
       <c r="Q21">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T21">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AA21">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB21">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC21">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD21">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.35</v>
+        <v>3.26</v>
       </c>
       <c r="O22">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q22">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="R22">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
+        <v>3.12</v>
+      </c>
+      <c r="U22">
+        <v>2.45</v>
+      </c>
+      <c r="V22">
+        <v>1.44</v>
+      </c>
+      <c r="W22">
+        <v>1.08</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
+        <v>1.22</v>
+      </c>
+      <c r="Z22">
+        <v>4.29</v>
+      </c>
+      <c r="AA22">
+        <v>1.65</v>
+      </c>
+      <c r="AB22">
+        <v>2.15</v>
+      </c>
+      <c r="AC22">
         <v>2.75</v>
       </c>
-      <c r="U22">
-        <v>3.14</v>
-      </c>
-      <c r="V22">
-        <v>1.34</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.28</v>
-      </c>
-      <c r="Z22">
-        <v>3.17</v>
-      </c>
-      <c r="AA22">
-        <v>2.15</v>
-      </c>
-      <c r="AB22">
-        <v>1.72</v>
-      </c>
-      <c r="AC22">
-        <v>3.34</v>
-      </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
+        <v>1.3</v>
+      </c>
+      <c r="AK22">
         <v>1.31</v>
-      </c>
-      <c r="AK22">
-        <v>1.55</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.26</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>4.29</v>
+        <v>3.42</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AB23">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AC23">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P24">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U24">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z24">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="AA24">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC24">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AD24">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>2.81</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB26">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC26">
         <v>3.84</v>
@@ -4716,7 +4716,7 @@
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
@@ -4749,10 +4749,10 @@
         <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
         <v>2.21</v>
@@ -4888,7 +4888,7 @@
         <v>2.38</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
         <v>3.38</v>
@@ -4900,25 +4900,25 @@
         <v>1.52</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z28">
         <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD28">
         <v>1.44</v>
@@ -4927,7 +4927,7 @@
         <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
         <v>2.25</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
         <v>2.05</v>
@@ -5075,10 +5075,10 @@
         <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC29">
         <v>2.41</v>
@@ -5238,7 +5238,7 @@
         <v>3.7</v>
       </c>
       <c r="AA30">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>3.53</v>
+        <v>4.82</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC31">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AD31">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="P32">
-        <v>4.82</v>
+        <v>3.53</v>
       </c>
       <c r="Q32">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R32">
+        <v>2.3</v>
+      </c>
+      <c r="S32">
+        <v>1.27</v>
+      </c>
+      <c r="T32">
+        <v>3.3</v>
+      </c>
+      <c r="U32">
+        <v>2.29</v>
+      </c>
+      <c r="V32">
+        <v>1.5</v>
+      </c>
+      <c r="W32">
+        <v>1.11</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.2</v>
+      </c>
+      <c r="Z32">
+        <v>4.44</v>
+      </c>
+      <c r="AA32">
+        <v>1.65</v>
+      </c>
+      <c r="AB32">
+        <v>2.15</v>
+      </c>
+      <c r="AC32">
         <v>2.51</v>
       </c>
-      <c r="S32">
-        <v>1.2</v>
-      </c>
-      <c r="T32">
-        <v>4</v>
-      </c>
-      <c r="U32">
-        <v>2.14</v>
-      </c>
-      <c r="V32">
-        <v>1.64</v>
-      </c>
-      <c r="W32">
-        <v>1.15</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.12</v>
-      </c>
-      <c r="Z32">
-        <v>4.7</v>
-      </c>
-      <c r="AA32">
-        <v>1.48</v>
-      </c>
-      <c r="AB32">
-        <v>2.33</v>
-      </c>
-      <c r="AC32">
-        <v>2.33</v>
-      </c>
       <c r="AD32">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AE32">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1456,25 +1456,25 @@
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q7">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="R7">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="U7">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1483,10 +1483,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AA7">
         <v>2.1</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
         <v>3.55</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
         <v>3.4</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,61 +3409,61 @@
         <v>2</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U19">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
+        <v>1.3</v>
+      </c>
+      <c r="Z19">
+        <v>2.97</v>
+      </c>
+      <c r="AA19">
+        <v>2.06</v>
+      </c>
+      <c r="AB19">
+        <v>1.71</v>
+      </c>
+      <c r="AC19">
+        <v>3.58</v>
+      </c>
+      <c r="AD19">
         <v>1.21</v>
       </c>
-      <c r="Z19">
-        <v>3.58</v>
-      </c>
-      <c r="AA19">
-        <v>1.8</v>
-      </c>
-      <c r="AB19">
-        <v>1.94</v>
-      </c>
-      <c r="AC19">
-        <v>2.92</v>
-      </c>
-      <c r="AD19">
-        <v>1.31</v>
-      </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P20">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="Q20">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="R20">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S20">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T20">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AA20">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC20">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.35</v>
+        <v>3.26</v>
       </c>
       <c r="O21">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q21">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="R21">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
+        <v>3.12</v>
+      </c>
+      <c r="U21">
+        <v>2.45</v>
+      </c>
+      <c r="V21">
+        <v>1.44</v>
+      </c>
+      <c r="W21">
+        <v>1.08</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>1.22</v>
+      </c>
+      <c r="Z21">
+        <v>4.29</v>
+      </c>
+      <c r="AA21">
+        <v>1.65</v>
+      </c>
+      <c r="AB21">
+        <v>2.15</v>
+      </c>
+      <c r="AC21">
         <v>2.75</v>
       </c>
-      <c r="U21">
-        <v>3.14</v>
-      </c>
-      <c r="V21">
-        <v>1.34</v>
-      </c>
-      <c r="W21">
-        <v>1.06</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.28</v>
-      </c>
-      <c r="Z21">
-        <v>3.17</v>
-      </c>
-      <c r="AA21">
-        <v>2.15</v>
-      </c>
-      <c r="AB21">
-        <v>1.72</v>
-      </c>
-      <c r="AC21">
-        <v>3.34</v>
-      </c>
       <c r="AD21">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
+        <v>1.3</v>
+      </c>
+      <c r="AK21">
         <v>1.31</v>
-      </c>
-      <c r="AK21">
-        <v>1.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.26</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P22">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.79</v>
+      </c>
+      <c r="AA22">
+        <v>1.9</v>
+      </c>
+      <c r="AB22">
+        <v>1.86</v>
+      </c>
+      <c r="AC22">
+        <v>3.22</v>
+      </c>
+      <c r="AD22">
+        <v>1.34</v>
+      </c>
+      <c r="AE22">
         <v>1.08</v>
       </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.22</v>
-      </c>
-      <c r="Z22">
-        <v>4.29</v>
-      </c>
-      <c r="AA22">
-        <v>1.65</v>
-      </c>
-      <c r="AB22">
-        <v>2.15</v>
-      </c>
-      <c r="AC22">
-        <v>2.75</v>
-      </c>
-      <c r="AD22">
-        <v>1.4</v>
-      </c>
-      <c r="AE22">
-        <v>1.14</v>
-      </c>
       <c r="AF22">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="R24">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="V24">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC24">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="AD24">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
+        <v>1.8</v>
+      </c>
+      <c r="O28">
+        <v>3.9</v>
+      </c>
+      <c r="P28">
+        <v>3.93</v>
+      </c>
+      <c r="Q28">
+        <v>2.3</v>
+      </c>
+      <c r="R28">
+        <v>2.33</v>
+      </c>
+      <c r="S28">
+        <v>1.26</v>
+      </c>
+      <c r="T28">
+        <v>3.4</v>
+      </c>
+      <c r="U28">
+        <v>2.23</v>
+      </c>
+      <c r="V28">
+        <v>1.56</v>
+      </c>
+      <c r="W28">
+        <v>1.12</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.15</v>
+      </c>
+      <c r="Z28">
+        <v>4.2</v>
+      </c>
+      <c r="AA28">
+        <v>1.57</v>
+      </c>
+      <c r="AB28">
+        <v>2.35</v>
+      </c>
+      <c r="AC28">
+        <v>2.41</v>
+      </c>
+      <c r="AD28">
+        <v>1.45</v>
+      </c>
+      <c r="AE28">
+        <v>1.15</v>
+      </c>
+      <c r="AF28">
         <v>1.65</v>
       </c>
-      <c r="O28">
-        <v>4</v>
-      </c>
-      <c r="P28">
-        <v>4.8</v>
-      </c>
-      <c r="Q28">
-        <v>2.1</v>
-      </c>
-      <c r="R28">
-        <v>2.38</v>
-      </c>
-      <c r="S28">
-        <v>1.29</v>
-      </c>
-      <c r="T28">
-        <v>3.38</v>
-      </c>
-      <c r="U28">
-        <v>2.32</v>
-      </c>
-      <c r="V28">
-        <v>1.52</v>
-      </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.13</v>
-      </c>
-      <c r="Z28">
-        <v>4.5</v>
-      </c>
-      <c r="AA28">
-        <v>1.58</v>
-      </c>
-      <c r="AB28">
+      <c r="AG28">
         <v>2.2</v>
       </c>
-      <c r="AC28">
-        <v>2.38</v>
-      </c>
-      <c r="AD28">
-        <v>1.44</v>
-      </c>
-      <c r="AE28">
-        <v>1.14</v>
-      </c>
-      <c r="AF28">
-        <v>1.57</v>
-      </c>
-      <c r="AG28">
-        <v>2.25</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.93</v>
+        <v>2.07</v>
       </c>
       <c r="Q29">
-        <v>2.3</v>
+        <v>3.88</v>
       </c>
       <c r="R29">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
         <v>1.26</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="V29">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB29">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC29">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AD29">
         <v>1.45</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.16</v>
+        <v>1.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,58 +5199,58 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.09</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="P30">
-        <v>2.07</v>
+        <v>3.53</v>
       </c>
       <c r="Q30">
-        <v>3.88</v>
+        <v>2.62</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="AA30">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AD30">
         <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U31">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V31">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AB31">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O32">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="P32">
-        <v>3.53</v>
+        <v>4.82</v>
       </c>
       <c r="Q32">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="S32">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z32">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AB32">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC32">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AD32">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>1.36</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P35">
         <v>7.9</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1655,7 +1655,7 @@
         <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>2.81</v>
@@ -2105,7 +2105,7 @@
         <v>1.59</v>
       </c>
       <c r="O11">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
         <v>4.77</v>
@@ -2763,55 +2763,55 @@
         <v>4.21</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="U15">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA15">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB15">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AC15">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
         <v>3.4</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3463,7 +3463,7 @@
         <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
         <v>2.45</v>
@@ -3768,7 +3768,7 @@
         <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="AA21">
         <v>1.65</v>
@@ -3937,7 +3937,7 @@
         <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
         <v>3.22</v>
@@ -3946,7 +3946,7 @@
         <v>1.34</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
         <v>1.7</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R23">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA23">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AC23">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AD23">
         <v>1.31</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q24">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="R24">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
         <v>3</v>
       </c>
       <c r="U24">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z24">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB24">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC24">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="AD24">
         <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AB27">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
         <v>2.21</v>
@@ -4761,7 +4761,7 @@
         <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB28">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC28">
         <v>2.41</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.09</v>
+        <v>1.65</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>2.07</v>
+        <v>4.75</v>
       </c>
       <c r="Q29">
-        <v>3.88</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="U29">
         <v>2.32</v>
@@ -5066,34 +5066,34 @@
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB29">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
         <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,43 +5199,43 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>3.09</v>
       </c>
       <c r="O30">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.53</v>
+        <v>2.07</v>
       </c>
       <c r="Q30">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.44</v>
+        <v>3.7</v>
       </c>
       <c r="AA30">
         <v>1.65</v>
@@ -5244,13 +5244,13 @@
         <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="AD30">
         <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
+        <v>1.25</v>
+      </c>
+      <c r="AK30">
         <v>1.3</v>
-      </c>
-      <c r="AK30">
-        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P31">
-        <v>4.8</v>
+        <v>3.53</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AA31">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5567,10 +5567,10 @@
         <v>1.48</v>
       </c>
       <c r="AB32">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC32">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD32">
         <v>1.6</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -964,7 +964,7 @@
         <v>2.1</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
         <v>3.24</v>
@@ -1456,22 +1456,22 @@
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="V7">
         <v>1.32</v>
@@ -1486,7 +1486,7 @@
         <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA7">
         <v>2.1</v>
@@ -1631,7 +1631,7 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U8">
         <v>2.47</v>
@@ -1948,7 +1948,7 @@
         <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
         <v>2.4</v>
@@ -1966,37 +1966,37 @@
         <v>1.62</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.09</v>
       </c>
       <c r="Z10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA10">
         <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC10">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG10">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="Q14">
         <v>3.09</v>
@@ -2612,7 +2612,7 @@
         <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
         <v>1.5</v>
@@ -2627,28 +2627,28 @@
         <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC14">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="AD14">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
         <v>2.1</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O17">
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
         <v>2.18</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -3460,7 +3460,7 @@
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
         <v>1.87</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
         <v>3.22</v>
       </c>
       <c r="P22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
         <v>2.78</v>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
         <v>2.8</v>
@@ -4586,10 +4586,10 @@
         <v>2.81</v>
       </c>
       <c r="AA26">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB26">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC26">
         <v>3.84</v>
@@ -4755,7 +4755,7 @@
         <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
         <v>1.61</v>
@@ -5078,7 +5078,7 @@
         <v>1.58</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC29">
         <v>2.38</v>
@@ -6180,7 +6180,7 @@
         <v>4.2</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
         <v>1.75</v>
@@ -6195,13 +6195,13 @@
         <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
         <v>1.12</v>
@@ -6216,19 +6216,19 @@
         <v>4.05</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB36">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD36">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
         <v>1.67</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -665,7 +665,7 @@
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.14</v>
@@ -967,7 +967,7 @@
         <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1631,7 +1631,7 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
         <v>2.47</v>
@@ -1652,7 +1652,7 @@
         <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
         <v>2</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.36</v>
@@ -1815,10 +1815,10 @@
         <v>6.9</v>
       </c>
       <c r="AA9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB9">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AC9">
         <v>1.67</v>
@@ -1948,7 +1948,7 @@
         <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
         <v>2.4</v>
@@ -1960,43 +1960,43 @@
         <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA10">
         <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD10">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE10">
         <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG10">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O14">
         <v>3.42</v>
@@ -2621,7 +2621,7 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.19</v>
@@ -2636,10 +2636,10 @@
         <v>2.13</v>
       </c>
       <c r="AC14">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="P15">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.23</v>
       </c>
       <c r="T15">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>2.55</v>
@@ -2781,7 +2781,7 @@
         <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -3101,10 +3101,10 @@
         <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3122,7 +3122,7 @@
         <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
         <v>2.56</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
         <v>1.73</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
         <v>3.6</v>
@@ -3267,7 +3267,7 @@
         <v>2.55</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W18">
         <v>1.09</v>
@@ -3282,10 +3282,10 @@
         <v>4.05</v>
       </c>
       <c r="AA18">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC18">
         <v>2.75</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3421,7 +3421,7 @@
         <v>2.02</v>
       </c>
       <c r="S19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>2.71</v>
@@ -3433,7 +3433,7 @@
         <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3460,7 +3460,7 @@
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
         <v>1.87</v>
@@ -3479,7 +3479,7 @@
         <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>2.03</v>
       </c>
       <c r="S20">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T20">
         <v>2.75</v>
@@ -3611,7 +3611,7 @@
         <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC20">
         <v>3.34</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="O21">
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>3.6</v>
@@ -3759,7 +3759,7 @@
         <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.04</v>
@@ -3771,7 +3771,7 @@
         <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
         <v>2.15</v>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O22">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="P22">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="Q22">
         <v>2.78</v>
       </c>
       <c r="R22">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3937,7 +3937,7 @@
         <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC22">
         <v>3.22</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
         <v>1.6</v>
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="O23">
         <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R23">
         <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
         <v>3</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4100,7 +4100,7 @@
         <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
         <v>2.92</v>
@@ -4131,7 +4131,7 @@
         <v>1.27</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="P24">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q24">
         <v>2.93</v>
@@ -4236,13 +4236,13 @@
         <v>2.22</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V24">
         <v>1.4</v>
@@ -4393,56 +4393,56 @@
         <v>6.5</v>
       </c>
       <c r="Q25">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="R25">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="S25">
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
+        <v>2.18</v>
+      </c>
+      <c r="V25">
+        <v>1.62</v>
+      </c>
+      <c r="W25">
+        <v>1.15</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.12</v>
+      </c>
+      <c r="Z25">
+        <v>4.65</v>
+      </c>
+      <c r="AA25">
+        <v>1.48</v>
+      </c>
+      <c r="AB25">
+        <v>2.33</v>
+      </c>
+      <c r="AC25">
         <v>2.24</v>
       </c>
-      <c r="V25">
-        <v>1.57</v>
-      </c>
-      <c r="W25">
-        <v>1.14</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.1</v>
-      </c>
-      <c r="Z25">
-        <v>3.4</v>
-      </c>
-      <c r="AA25">
-        <v>1.53</v>
-      </c>
-      <c r="AB25">
-        <v>2.28</v>
-      </c>
-      <c r="AC25">
-        <v>2.38</v>
-      </c>
       <c r="AD25">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
+        <v>1.95</v>
+      </c>
+      <c r="AG25">
         <v>1.75</v>
       </c>
-      <c r="AG25">
-        <v>1.95</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK25">
-        <v>3</v>
+        <v>3.84</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>2</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
         <v>2.61</v>
@@ -4589,7 +4589,7 @@
         <v>2.2</v>
       </c>
       <c r="AB26">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC26">
         <v>3.84</v>
@@ -4882,55 +4882,55 @@
         <v>3.93</v>
       </c>
       <c r="Q28">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="R28">
+        <v>2.46</v>
+      </c>
+      <c r="S28">
+        <v>1.25</v>
+      </c>
+      <c r="T28">
+        <v>3.7</v>
+      </c>
+      <c r="U28">
+        <v>2.15</v>
+      </c>
+      <c r="V28">
+        <v>1.6</v>
+      </c>
+      <c r="W28">
+        <v>1.13</v>
+      </c>
+      <c r="X28">
+        <v>1.02</v>
+      </c>
+      <c r="Y28">
+        <v>1.12</v>
+      </c>
+      <c r="Z28">
+        <v>4.8</v>
+      </c>
+      <c r="AA28">
+        <v>1.5</v>
+      </c>
+      <c r="AB28">
         <v>2.33</v>
       </c>
-      <c r="S28">
-        <v>1.26</v>
-      </c>
-      <c r="T28">
-        <v>3.4</v>
-      </c>
-      <c r="U28">
+      <c r="AC28">
         <v>2.23</v>
       </c>
-      <c r="V28">
-        <v>1.56</v>
-      </c>
-      <c r="W28">
-        <v>1.12</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.15</v>
-      </c>
-      <c r="Z28">
-        <v>4.2</v>
-      </c>
-      <c r="AA28">
-        <v>1.6</v>
-      </c>
-      <c r="AB28">
-        <v>2.3</v>
-      </c>
-      <c r="AC28">
-        <v>2.41</v>
-      </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>3.09</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.75</v>
+        <v>2.07</v>
       </c>
       <c r="Q29">
-        <v>2.1</v>
+        <v>3.88</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
         <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
         <v>2.32</v>
@@ -5066,34 +5066,34 @@
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA29">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB29">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AD29">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE29">
         <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,58 +5199,58 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.09</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="P30">
-        <v>2.07</v>
+        <v>3.53</v>
       </c>
       <c r="Q30">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.7</v>
+        <v>4.44</v>
       </c>
       <c r="AA30">
         <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD30">
         <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>3.53</v>
+        <v>4.82</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U31">
+        <v>2.12</v>
+      </c>
+      <c r="V31">
+        <v>1.65</v>
+      </c>
+      <c r="W31">
+        <v>1.17</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.12</v>
+      </c>
+      <c r="Z31">
+        <v>4.8</v>
+      </c>
+      <c r="AA31">
+        <v>1.47</v>
+      </c>
+      <c r="AB31">
+        <v>2.63</v>
+      </c>
+      <c r="AC31">
         <v>2.29</v>
       </c>
-      <c r="V31">
-        <v>1.5</v>
-      </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.2</v>
-      </c>
-      <c r="Z31">
-        <v>4.44</v>
-      </c>
-      <c r="AA31">
-        <v>1.65</v>
-      </c>
-      <c r="AB31">
-        <v>2.15</v>
-      </c>
-      <c r="AC31">
-        <v>2.51</v>
-      </c>
       <c r="AD31">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE31">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O32">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="Q32">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U32">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AB32">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AC32">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AD32">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>4.9</v>
       </c>
       <c r="P35">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>1.83</v>
@@ -6059,13 +6059,13 @@
         <v>2.18</v>
       </c>
       <c r="AC35">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
         <v>1.45</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
         <v>2</v>
@@ -6183,7 +6183,7 @@
         <v>3.9</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q36">
         <v>4.24</v>
@@ -6367,7 +6367,7 @@
         <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6379,13 +6379,13 @@
         <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC37">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="AD37">
         <v>1.22</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1480,7 +1480,7 @@
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
         <v>1.38</v>
@@ -1495,10 +1495,10 @@
         <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
         <v>1.04</v>
@@ -1960,7 +1960,7 @@
         <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="V10">
         <v>1.67</v>
@@ -1975,7 +1975,7 @@
         <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA10">
         <v>1.5</v>
@@ -1984,19 +1984,19 @@
         <v>2.59</v>
       </c>
       <c r="AC10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AD10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE10">
         <v>1.25</v>
       </c>
       <c r="AF10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG10">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>5.79</v>
+        <v>5.35</v>
       </c>
       <c r="R13">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2449,43 +2449,43 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="V13">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
         <v>1.07</v>
       </c>
       <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>1.35</v>
+      </c>
+      <c r="Z13">
+        <v>2.74</v>
+      </c>
+      <c r="AA13">
+        <v>2.22</v>
+      </c>
+      <c r="AB13">
+        <v>1.64</v>
+      </c>
+      <c r="AC13">
+        <v>4.03</v>
+      </c>
+      <c r="AD13">
+        <v>1.22</v>
+      </c>
+      <c r="AE13">
         <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>1.34</v>
-      </c>
-      <c r="Z13">
-        <v>2.78</v>
-      </c>
-      <c r="AA13">
-        <v>2.17</v>
-      </c>
-      <c r="AB13">
-        <v>1.67</v>
-      </c>
-      <c r="AC13">
-        <v>3.9</v>
-      </c>
-      <c r="AD13">
-        <v>1.23</v>
-      </c>
-      <c r="AE13">
-        <v>1.04</v>
       </c>
       <c r="AF13">
         <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="O14">
         <v>3.42</v>
@@ -2600,16 +2600,16 @@
         <v>2.23</v>
       </c>
       <c r="Q14">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U14">
         <v>2.45</v>
@@ -2618,10 +2618,10 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.19</v>
@@ -2636,10 +2636,10 @@
         <v>2.13</v>
       </c>
       <c r="AC14">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="Q15">
         <v>2.25</v>
@@ -2769,7 +2769,7 @@
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
         <v>3.3</v>
@@ -3107,7 +3107,7 @@
         <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3246,10 +3246,10 @@
         <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
         <v>3.61</v>
@@ -3258,7 +3258,7 @@
         <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
         <v>3.25</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P19">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AA19">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC19">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.35</v>
+        <v>3.26</v>
       </c>
       <c r="O20">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="Q20">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="R20">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
+        <v>3.25</v>
+      </c>
+      <c r="U20">
+        <v>2.45</v>
+      </c>
+      <c r="V20">
+        <v>1.44</v>
+      </c>
+      <c r="W20">
+        <v>1.11</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>1.22</v>
+      </c>
+      <c r="Z20">
+        <v>4.3</v>
+      </c>
+      <c r="AA20">
+        <v>1.65</v>
+      </c>
+      <c r="AB20">
+        <v>2.15</v>
+      </c>
+      <c r="AC20">
         <v>2.75</v>
       </c>
-      <c r="U20">
-        <v>3.14</v>
-      </c>
-      <c r="V20">
-        <v>1.34</v>
-      </c>
-      <c r="W20">
-        <v>1.06</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.28</v>
-      </c>
-      <c r="Z20">
-        <v>3.17</v>
-      </c>
-      <c r="AA20">
-        <v>2.15</v>
-      </c>
-      <c r="AB20">
+      <c r="AD20">
+        <v>1.4</v>
+      </c>
+      <c r="AE20">
+        <v>1.14</v>
+      </c>
+      <c r="AF20">
+        <v>1.57</v>
+      </c>
+      <c r="AG20">
+        <v>2.25</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.67</v>
       </c>
-      <c r="AC20">
-        <v>3.34</v>
-      </c>
-      <c r="AD20">
-        <v>1.24</v>
-      </c>
-      <c r="AE20">
-        <v>1.05</v>
-      </c>
-      <c r="AF20">
-        <v>1.76</v>
-      </c>
-      <c r="AG20">
-        <v>1.96</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.33</v>
-      </c>
       <c r="AK20">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.11</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
+        <v>1.8</v>
+      </c>
+      <c r="AB22">
         <v>1.9</v>
       </c>
-      <c r="AB22">
-        <v>1.84</v>
-      </c>
       <c r="AC22">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="AD22">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
+        <v>1.66</v>
+      </c>
+      <c r="AG22">
+        <v>2.09</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.27</v>
+      </c>
+      <c r="AK22">
         <v>1.7</v>
-      </c>
-      <c r="AG22">
-        <v>2.05</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.3</v>
-      </c>
-      <c r="AK22">
-        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q23">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="R23">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="AD23">
         <v>1.31</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="R24">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U24">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.3</v>
+      </c>
+      <c r="Z24">
+        <v>2.97</v>
+      </c>
+      <c r="AA24">
+        <v>2.06</v>
+      </c>
+      <c r="AB24">
+        <v>1.71</v>
+      </c>
+      <c r="AC24">
+        <v>3.58</v>
+      </c>
+      <c r="AD24">
+        <v>1.21</v>
+      </c>
+      <c r="AE24">
         <v>1.03</v>
       </c>
-      <c r="Y24">
-        <v>1.23</v>
-      </c>
-      <c r="Z24">
-        <v>3.42</v>
-      </c>
-      <c r="AA24">
+      <c r="AF24">
+        <v>1.9</v>
+      </c>
+      <c r="AG24">
         <v>1.87</v>
       </c>
-      <c r="AB24">
-        <v>1.84</v>
-      </c>
-      <c r="AC24">
-        <v>3.43</v>
-      </c>
-      <c r="AD24">
-        <v>1.31</v>
-      </c>
-      <c r="AE24">
-        <v>1.06</v>
-      </c>
-      <c r="AF24">
-        <v>1.73</v>
-      </c>
-      <c r="AG24">
-        <v>2</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK24">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>1.98</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="P27">
         <v>3.19</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3.93</v>
+        <v>2.07</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="R28">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
+        <v>1.29</v>
+      </c>
+      <c r="T28">
+        <v>3.6</v>
+      </c>
+      <c r="U28">
+        <v>2.32</v>
+      </c>
+      <c r="V28">
+        <v>1.52</v>
+      </c>
+      <c r="W28">
+        <v>1.11</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.2</v>
+      </c>
+      <c r="Z28">
+        <v>3.75</v>
+      </c>
+      <c r="AA28">
+        <v>1.63</v>
+      </c>
+      <c r="AB28">
+        <v>2.1</v>
+      </c>
+      <c r="AC28">
+        <v>2.56</v>
+      </c>
+      <c r="AD28">
+        <v>1.45</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.53</v>
+      </c>
+      <c r="AG28">
+        <v>2.3</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.25</v>
       </c>
-      <c r="T28">
-        <v>3.7</v>
-      </c>
-      <c r="U28">
-        <v>2.15</v>
-      </c>
-      <c r="V28">
-        <v>1.6</v>
-      </c>
-      <c r="W28">
-        <v>1.13</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.12</v>
-      </c>
-      <c r="Z28">
-        <v>4.8</v>
-      </c>
-      <c r="AA28">
-        <v>1.5</v>
-      </c>
-      <c r="AB28">
-        <v>2.33</v>
-      </c>
-      <c r="AC28">
-        <v>2.23</v>
-      </c>
-      <c r="AD28">
-        <v>1.57</v>
-      </c>
-      <c r="AE28">
-        <v>1.18</v>
-      </c>
-      <c r="AF28">
-        <v>1.59</v>
-      </c>
-      <c r="AG28">
-        <v>2.18</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.13</v>
-      </c>
       <c r="AK28">
-        <v>2.38</v>
+        <v>1.29</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.09</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="P29">
-        <v>2.07</v>
+        <v>3.53</v>
       </c>
       <c r="Q29">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
         <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA29">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB29">
         <v>2.1</v>
       </c>
       <c r="AC29">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="AD29">
         <v>1.45</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
         <v>1.53</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O30">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>3.53</v>
+        <v>4.75</v>
       </c>
       <c r="Q30">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="U30">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
+        <v>1.13</v>
+      </c>
+      <c r="Z30">
+        <v>4.5</v>
+      </c>
+      <c r="AA30">
+        <v>1.58</v>
+      </c>
+      <c r="AB30">
+        <v>2.27</v>
+      </c>
+      <c r="AC30">
+        <v>2.37</v>
+      </c>
+      <c r="AD30">
+        <v>1.44</v>
+      </c>
+      <c r="AE30">
+        <v>1.14</v>
+      </c>
+      <c r="AF30">
+        <v>1.57</v>
+      </c>
+      <c r="AG30">
+        <v>2.25</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.2</v>
       </c>
-      <c r="Z30">
-        <v>4.44</v>
-      </c>
-      <c r="AA30">
-        <v>1.65</v>
-      </c>
-      <c r="AB30">
-        <v>2.1</v>
-      </c>
-      <c r="AC30">
-        <v>2.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.45</v>
-      </c>
-      <c r="AE30">
-        <v>1.17</v>
-      </c>
-      <c r="AF30">
-        <v>1.53</v>
-      </c>
-      <c r="AG30">
-        <v>2.3</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.3</v>
-      </c>
       <c r="AK30">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="O31">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P31">
-        <v>4.82</v>
+        <v>3.93</v>
       </c>
       <c r="Q31">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="S31">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V31">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5401,25 +5401,25 @@
         <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB31">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="AC31">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AD31">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE31">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>1.59</v>
+      </c>
+      <c r="O32">
+        <v>3.95</v>
+      </c>
+      <c r="P32">
+        <v>4.82</v>
+      </c>
+      <c r="Q32">
+        <v>1.83</v>
+      </c>
+      <c r="R32">
+        <v>2.57</v>
+      </c>
+      <c r="S32">
+        <v>1.2</v>
+      </c>
+      <c r="T32">
+        <v>4</v>
+      </c>
+      <c r="U32">
+        <v>2.12</v>
+      </c>
+      <c r="V32">
         <v>1.65</v>
       </c>
-      <c r="O32">
-        <v>4</v>
-      </c>
-      <c r="P32">
-        <v>4.75</v>
-      </c>
-      <c r="Q32">
-        <v>2.1</v>
-      </c>
-      <c r="R32">
-        <v>2.38</v>
-      </c>
-      <c r="S32">
-        <v>1.29</v>
-      </c>
-      <c r="T32">
-        <v>3.38</v>
-      </c>
-      <c r="U32">
-        <v>2.32</v>
-      </c>
-      <c r="V32">
-        <v>1.52</v>
-      </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z32">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA32">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK32">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O33">
         <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P34">
         <v>3.35</v>
@@ -6059,7 +6059,7 @@
         <v>2.18</v>
       </c>
       <c r="AC35">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD35">
         <v>1.45</v>
@@ -6087,7 +6087,7 @@
         <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>1.77</v>
       </c>
       <c r="Q36">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="R36">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.3</v>
@@ -6228,7 +6228,7 @@
         <v>1.46</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
         <v>1.67</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -967,7 +967,7 @@
         <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2437,10 +2437,10 @@
         <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="R13">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2449,7 +2449,7 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="V13">
         <v>1.31</v>
@@ -2458,7 +2458,7 @@
         <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
         <v>1.35</v>
@@ -2467,19 +2467,19 @@
         <v>2.74</v>
       </c>
       <c r="AA13">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AB13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="AD13">
         <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>2</v>
@@ -2594,13 +2594,13 @@
         <v>2.89</v>
       </c>
       <c r="O14">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
         <v>2.23</v>
       </c>
       <c r="Q14">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="R14">
         <v>2.2</v>
@@ -2621,7 +2621,7 @@
         <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.19</v>
@@ -2636,10 +2636,10 @@
         <v>2.13</v>
       </c>
       <c r="AC14">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
@@ -2648,7 +2648,7 @@
         <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>1.48</v>
       </c>
       <c r="AB25">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC25">
         <v>2.24</v>
@@ -6017,10 +6017,10 @@
         <v>1.36</v>
       </c>
       <c r="O35">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="Q35">
         <v>1.83</v>
@@ -6053,16 +6053,16 @@
         <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AC35">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE35">
         <v>1.13</v>
@@ -6183,7 +6183,7 @@
         <v>3.9</v>
       </c>
       <c r="P36">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="Q36">
         <v>4.1</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="Q37">
         <v>2.69</v>
@@ -6382,7 +6382,7 @@
         <v>2.13</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
         <v>3.73</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -638,16 +638,16 @@
         <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
+        <v>2.2</v>
+      </c>
+      <c r="Q2">
+        <v>3.02</v>
+      </c>
+      <c r="R2">
         <v>2.14</v>
-      </c>
-      <c r="Q2">
-        <v>3.48</v>
-      </c>
-      <c r="R2">
-        <v>2.12</v>
       </c>
       <c r="S2">
         <v>1.29</v>
@@ -665,7 +665,7 @@
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.14</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1658,16 +1658,16 @@
         <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
         <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
         <v>2.2</v>
@@ -1821,10 +1821,10 @@
         <v>3.8</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD9">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE9">
         <v>1.45</v>
@@ -1948,10 +1948,10 @@
         <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S10">
         <v>1.22</v>
@@ -1960,7 +1960,7 @@
         <v>3.75</v>
       </c>
       <c r="U10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V10">
         <v>1.67</v>
@@ -1975,22 +1975,22 @@
         <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA10">
         <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AC10">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD10">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
         <v>1.4</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="O11">
         <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="Q11">
         <v>2.2</v>
@@ -2132,7 +2132,7 @@
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="O14">
         <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q14">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.45</v>
@@ -2618,22 +2618,22 @@
         <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AC14">
         <v>2.7</v>
@@ -2642,7 +2642,7 @@
         <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.56</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q15">
         <v>2.25</v>
@@ -2775,7 +2775,7 @@
         <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V15">
         <v>1.49</v>
@@ -2784,28 +2784,28 @@
         <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
         <v>1.59</v>
       </c>
       <c r="AB15">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AC15">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
         <v>1.59</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
@@ -2947,13 +2947,13 @@
         <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
@@ -2962,13 +2962,13 @@
         <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
         <v>1.65</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O17">
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
         <v>2.55</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
         <v>1.28</v>
@@ -3113,10 +3113,10 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA17">
         <v>1.67</v>
@@ -3125,19 +3125,19 @@
         <v>2.15</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
+        <v>2.17</v>
+      </c>
+      <c r="Q18">
+        <v>3.28</v>
+      </c>
+      <c r="R18">
         <v>2.2</v>
-      </c>
-      <c r="Q18">
-        <v>3.61</v>
-      </c>
-      <c r="R18">
-        <v>2.25</v>
       </c>
       <c r="S18">
         <v>1.27</v>
@@ -3267,34 +3267,34 @@
         <v>2.55</v>
       </c>
       <c r="V18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
         <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB18">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3424,7 +3424,7 @@
         <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
         <v>3.14</v>
@@ -3436,31 +3436,31 @@
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB19">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AD19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
         <v>1.96</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
         <v>3.6</v>
@@ -3581,10 +3581,10 @@
         <v>3.6</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
         <v>3.25</v>
@@ -3599,22 +3599,22 @@
         <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
         <v>1.4</v>
@@ -3626,7 +3626,7 @@
         <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AK20">
         <v>1.3</v>
@@ -3738,16 +3738,16 @@
         <v>3.2</v>
       </c>
       <c r="P21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
         <v>2.7</v>
@@ -3756,40 +3756,40 @@
         <v>2.7</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
         <v>1.92</v>
       </c>
       <c r="AB21">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AD21">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
         <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q22">
         <v>2.47</v>
@@ -3925,28 +3925,28 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
         <v>1.66</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
         <v>1.7</v>
@@ -4064,7 +4064,7 @@
         <v>3.1</v>
       </c>
       <c r="P23">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q23">
         <v>2.91</v>
@@ -4088,34 +4088,34 @@
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z23">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC23">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AD23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
         <v>1.59</v>
@@ -4233,7 +4233,7 @@
         <v>2.62</v>
       </c>
       <c r="R24">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="S24">
         <v>1.4</v>
@@ -4251,31 +4251,31 @@
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA24">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG24">
         <v>1.87</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
         <v>1.75</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="O25">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4553,7 +4553,7 @@
         <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
@@ -4719,10 +4719,10 @@
         <v>3.19</v>
       </c>
       <c r="Q27">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
         <v>1.18</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
         <v>3.85</v>
@@ -5217,7 +5217,7 @@
         <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
         <v>2.32</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK30">
         <v>2.05</v>
@@ -5534,7 +5534,7 @@
         <v>4.82</v>
       </c>
       <c r="Q32">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R32">
         <v>2.57</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P35">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q35">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R35">
+        <v>2.46</v>
+      </c>
+      <c r="S35">
+        <v>1.32</v>
+      </c>
+      <c r="T35">
+        <v>3.2</v>
+      </c>
+      <c r="U35">
         <v>2.43</v>
       </c>
-      <c r="S35">
-        <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3.14</v>
-      </c>
-      <c r="U35">
-        <v>2.51</v>
-      </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA35">
         <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC35">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="AD35">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG35">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
         <v>3.9</v>
       </c>
       <c r="P36">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Q36">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S36">
         <v>1.3</v>
@@ -6216,16 +6216,16 @@
         <v>4.05</v>
       </c>
       <c r="AA36">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC36">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AD36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
         <v>1.17</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6370,13 +6370,13 @@
         <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
         <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA37">
         <v>2.13</v>
@@ -6391,13 +6391,13 @@
         <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1003,7 +1003,7 @@
         <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1480,7 +1480,7 @@
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.38</v>
@@ -1495,10 +1495,10 @@
         <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
         <v>1.04</v>
@@ -1818,7 +1818,7 @@
         <v>1.29</v>
       </c>
       <c r="AB9">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC9">
         <v>1.73</v>
@@ -2114,7 +2114,7 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
@@ -3086,10 +3086,10 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q17">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="R17">
         <v>2.25</v>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>1.22</v>
       </c>
       <c r="O25">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P25">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4722,7 +4722,7 @@
         <v>2.38</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
         <v>1.18</v>
@@ -4749,19 +4749,19 @@
         <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB27">
         <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD27">
         <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
         <v>1.7</v>
@@ -4885,7 +4885,7 @@
         <v>3.88</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S28">
         <v>1.29</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O30">
         <v>3.85</v>
@@ -5241,7 +5241,7 @@
         <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
         <v>2.37</v>
@@ -5386,7 +5386,7 @@
         <v>2.15</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
         <v>1.13</v>
@@ -5401,7 +5401,7 @@
         <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB31">
         <v>2.33</v>
@@ -5567,7 +5567,7 @@
         <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC32">
         <v>2.23</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O33">
         <v>3.75</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O34">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>3.35</v>
+        <v>2.91</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -2108,7 +2108,7 @@
         <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
         <v>2.2</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>3.25</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
         <v>3.28</v>
@@ -3282,7 +3282,7 @@
         <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB18">
         <v>2.07</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
+        <v>2.2</v>
+      </c>
+      <c r="O20">
         <v>3.2</v>
       </c>
-      <c r="O20">
-        <v>3.6</v>
-      </c>
       <c r="P20">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
-        <v>3.6</v>
+        <v>2.59</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
+        <v>2.7</v>
+      </c>
+      <c r="U20">
+        <v>2.7</v>
+      </c>
+      <c r="V20">
+        <v>1.42</v>
+      </c>
+      <c r="W20">
+        <v>1.06</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.5</v>
+      </c>
+      <c r="AA20">
+        <v>1.92</v>
+      </c>
+      <c r="AB20">
+        <v>1.9</v>
+      </c>
+      <c r="AC20">
         <v>3.25</v>
       </c>
-      <c r="U20">
-        <v>2.45</v>
-      </c>
-      <c r="V20">
-        <v>1.44</v>
-      </c>
-      <c r="W20">
-        <v>1.11</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.2</v>
-      </c>
-      <c r="Z20">
-        <v>4.33</v>
-      </c>
-      <c r="AA20">
+      <c r="AD20">
+        <v>1.33</v>
+      </c>
+      <c r="AE20">
+        <v>1.1</v>
+      </c>
+      <c r="AF20">
         <v>1.7</v>
       </c>
-      <c r="AB20">
+      <c r="AG20">
         <v>2.1</v>
       </c>
-      <c r="AC20">
-        <v>2.88</v>
-      </c>
-      <c r="AD20">
-        <v>1.4</v>
-      </c>
-      <c r="AE20">
-        <v>1.14</v>
-      </c>
-      <c r="AF20">
-        <v>1.57</v>
-      </c>
-      <c r="AG20">
-        <v>2.3</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="R21">
         <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.04</v>
@@ -3771,10 +3771,10 @@
         <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC21">
         <v>3.25</v>
@@ -3786,10 +3786,10 @@
         <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
         <v>1.7</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V22">
         <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
         <v>1.04</v>
@@ -3934,25 +3934,25 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC22">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="O23">
         <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="R23">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y23">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
+        <v>1.84</v>
+      </c>
+      <c r="AG23">
+        <v>1.87</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.21</v>
+      </c>
+      <c r="AK23">
         <v>1.75</v>
-      </c>
-      <c r="AG23">
-        <v>2.05</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.27</v>
-      </c>
-      <c r="AK23">
-        <v>1.59</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="Q24">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S24">
+        <v>1.31</v>
+      </c>
+      <c r="T24">
+        <v>3.25</v>
+      </c>
+      <c r="U24">
+        <v>2.45</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.11</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.2</v>
+      </c>
+      <c r="Z24">
+        <v>4.33</v>
+      </c>
+      <c r="AA24">
+        <v>1.7</v>
+      </c>
+      <c r="AB24">
+        <v>2.1</v>
+      </c>
+      <c r="AC24">
+        <v>2.88</v>
+      </c>
+      <c r="AD24">
         <v>1.4</v>
       </c>
-      <c r="T24">
-        <v>2.71</v>
-      </c>
-      <c r="U24">
-        <v>2.88</v>
-      </c>
-      <c r="V24">
-        <v>1.35</v>
-      </c>
-      <c r="W24">
-        <v>1.07</v>
-      </c>
-      <c r="X24">
-        <v>1.06</v>
-      </c>
-      <c r="Y24">
-        <v>1.36</v>
-      </c>
-      <c r="Z24">
-        <v>3.1</v>
-      </c>
-      <c r="AA24">
-        <v>2.15</v>
-      </c>
-      <c r="AB24">
-        <v>1.66</v>
-      </c>
-      <c r="AC24">
-        <v>4.1</v>
-      </c>
-      <c r="AD24">
-        <v>1.22</v>
-      </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -964,10 +964,10 @@
         <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q7">
         <v>2.29</v>
@@ -1465,16 +1465,16 @@
         <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U7">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1486,7 +1486,7 @@
         <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AA7">
         <v>2.1</v>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.16</v>
+      </c>
+      <c r="O9">
+        <v>6.6</v>
+      </c>
+      <c r="P9">
+        <v>10.5</v>
+      </c>
+      <c r="Q9">
+        <v>1.55</v>
+      </c>
+      <c r="R9">
+        <v>2.88</v>
+      </c>
+      <c r="S9">
         <v>1.14</v>
       </c>
-      <c r="O9">
-        <v>6.4</v>
-      </c>
-      <c r="P9">
-        <v>11</v>
-      </c>
-      <c r="Q9">
-        <v>1.52</v>
-      </c>
-      <c r="R9">
-        <v>2.93</v>
-      </c>
-      <c r="S9">
-        <v>1.13</v>
-      </c>
       <c r="T9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V9">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,28 +1812,28 @@
         <v>1.04</v>
       </c>
       <c r="Z9">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="AA9">
         <v>1.29</v>
       </c>
       <c r="AB9">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AC9">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AD9">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AE9">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG9">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.06</v>
       </c>
       <c r="AK9">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.09</v>
+        <v>3.95</v>
       </c>
       <c r="O10">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>2.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
         <v>3.92</v>
@@ -4423,7 +4423,7 @@
         <v>4.65</v>
       </c>
       <c r="AA25">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB25">
         <v>2.37</v>
@@ -4589,7 +4589,7 @@
         <v>2.2</v>
       </c>
       <c r="AB26">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC26">
         <v>3.84</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="O27">
-        <v>3.82</v>
+        <v>3.47</v>
       </c>
       <c r="P27">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="Q27">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
         <v>2.4</v>
@@ -4749,13 +4749,13 @@
         <v>5.25</v>
       </c>
       <c r="AA27">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
         <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD27">
         <v>1.61</v>
@@ -5241,7 +5241,7 @@
         <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC30">
         <v>2.37</v>
@@ -5401,7 +5401,7 @@
         <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB31">
         <v>2.33</v>
@@ -5567,7 +5567,7 @@
         <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
         <v>2.23</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1652,7 +1652,7 @@
         <v>3.8</v>
       </c>
       <c r="AA8">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
         <v>2</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>3.6</v>
@@ -2600,25 +2600,25 @@
         <v>2.15</v>
       </c>
       <c r="Q14">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2664,7 +2664,7 @@
         <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.24</v>
       </c>
       <c r="P19">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="Q19">
         <v>2.98</v>
@@ -3421,7 +3421,7 @@
         <v>2.03</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>2.7</v>
@@ -3448,7 +3448,7 @@
         <v>2.16</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC19">
         <v>4.1</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>3.3</v>
@@ -3771,7 +3771,7 @@
         <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
         <v>1.95</v>
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
         <v>2.23</v>
@@ -3913,7 +3913,7 @@
         <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="U22">
         <v>2.8</v>
@@ -3934,10 +3934,10 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB22">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
         <v>3.4</v>
@@ -4067,10 +4067,10 @@
         <v>3.5</v>
       </c>
       <c r="Q23">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R23">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="S23">
         <v>1.4</v>
@@ -4097,10 +4097,10 @@
         <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB23">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC23">
         <v>4.1</v>
@@ -4263,7 +4263,7 @@
         <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -6186,10 +6186,10 @@
         <v>1.75</v>
       </c>
       <c r="Q36">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="R36">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.3</v>
@@ -6216,16 +6216,16 @@
         <v>4.05</v>
       </c>
       <c r="AA36">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB36">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AC36">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
         <v>1.17</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -641,7 +641,7 @@
         <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
         <v>3.02</v>
@@ -1003,7 +1003,7 @@
         <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>3.2</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1459,10 +1459,10 @@
         <v>4.8</v>
       </c>
       <c r="Q7">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R7">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.44</v>
@@ -1477,7 +1477,7 @@
         <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.04</v>
@@ -1501,13 +1501,13 @@
         <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>4.33</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
         <v>1.67</v>
@@ -2449,7 +2449,7 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="V13">
         <v>1.31</v>
@@ -2464,16 +2464,16 @@
         <v>1.35</v>
       </c>
       <c r="Z13">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA13">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AB13">
         <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="AD13">
         <v>1.22</v>
@@ -2482,10 +2482,10 @@
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O14">
         <v>3.6</v>
@@ -2606,10 +2606,10 @@
         <v>2.32</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
         <v>2.15</v>
@@ -2618,7 +2618,7 @@
         <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2664,7 +2664,7 @@
         <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,49 +2754,49 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="R15">
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
         <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
         <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB15">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
         <v>2.7</v>
@@ -2805,10 +2805,10 @@
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
         <v>2.18</v>
@@ -2827,7 +2827,7 @@
         <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3412,22 +3412,22 @@
         <v>3.24</v>
       </c>
       <c r="P19">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q19">
         <v>2.98</v>
       </c>
       <c r="R19">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V19">
         <v>1.34</v>
@@ -3445,7 +3445,7 @@
         <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AB19">
         <v>1.66</v>
@@ -3454,13 +3454,13 @@
         <v>4.1</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
         <v>1.96</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O20">
         <v>3.2</v>
@@ -3578,31 +3578,31 @@
         <v>3.15</v>
       </c>
       <c r="Q20">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U20">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
         <v>3.5</v>
@@ -3611,19 +3611,19 @@
         <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC20">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
         <v>2.1</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,16 +3735,16 @@
         <v>2</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q21">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
         <v>1.33</v>
@@ -3753,10 +3753,10 @@
         <v>3</v>
       </c>
       <c r="U21">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
         <v>1.07</v>
@@ -3774,10 +3774,10 @@
         <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC21">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD21">
         <v>1.33</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
+        <v>3.2</v>
+      </c>
+      <c r="P22">
         <v>3.1</v>
       </c>
-      <c r="P22">
-        <v>3</v>
-      </c>
       <c r="Q22">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
         <v>2.23</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="U22">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA22">
         <v>1.87</v>
@@ -3949,7 +3949,7 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
         <v>2.05</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O23">
         <v>3.1</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
         <v>2.47</v>
       </c>
       <c r="R23">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
         <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="U23">
         <v>2.88</v>
@@ -4085,10 +4085,10 @@
         <v>1.35</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.36</v>
@@ -4103,19 +4103,19 @@
         <v>1.71</v>
       </c>
       <c r="AC23">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="AD23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG23">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
         <v>1.31</v>
@@ -4260,7 +4260,7 @@
         <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB24">
         <v>2.14</v>
@@ -4275,10 +4275,10 @@
         <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.76</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O35">
         <v>5.25</v>
@@ -6056,7 +6056,7 @@
         <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC35">
         <v>2.69</v>
@@ -6068,7 +6068,7 @@
         <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
         <v>1.76</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>1.12</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.19</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -638,7 +638,7 @@
         <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="P2">
         <v>2.14</v>
@@ -653,7 +653,7 @@
         <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U2">
         <v>2.38</v>
@@ -662,7 +662,7 @@
         <v>1.53</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -671,19 +671,19 @@
         <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA2">
         <v>1.57</v>
       </c>
       <c r="AB2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AD2">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N4">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
         <v>2.2</v>
@@ -1625,16 +1625,16 @@
         <v>3.4</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
         <v>1.46</v>
@@ -1655,7 +1655,7 @@
         <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
         <v>2.88</v>
@@ -1667,10 +1667,10 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1794,16 +1794,16 @@
         <v>1.14</v>
       </c>
       <c r="T9">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V9">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="W9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1815,16 +1815,16 @@
         <v>6.75</v>
       </c>
       <c r="AA9">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AB9">
         <v>3.2</v>
       </c>
       <c r="AC9">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AD9">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AE9">
         <v>1.43</v>
@@ -1945,22 +1945,22 @@
         <v>3.85</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>2.83</v>
       </c>
       <c r="Q10">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="R10">
         <v>2.41</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
         <v>1.67</v>
@@ -2012,7 +2012,7 @@
         <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O11">
         <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U11">
         <v>2.45</v>
@@ -2923,7 +2923,7 @@
         <v>3.38</v>
       </c>
       <c r="P16">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q16">
         <v>3.14</v>
@@ -2932,13 +2932,13 @@
         <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
         <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2953,16 +2953,16 @@
         <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA16">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
         <v>1.36</v>
@@ -2971,7 +2971,7 @@
         <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG16">
         <v>2.1</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
         <v>1.44</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
         <v>3.25</v>
@@ -3104,7 +3104,7 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3119,10 +3119,10 @@
         <v>4.33</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC17">
         <v>2.88</v>
@@ -3131,7 +3131,7 @@
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
         <v>1.6</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q18">
         <v>3.28</v>
@@ -3264,10 +3264,10 @@
         <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
         <v>1.09</v>
@@ -3282,19 +3282,19 @@
         <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB18">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC18">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
         <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -4399,16 +4399,16 @@
         <v>2.71</v>
       </c>
       <c r="S25">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="V25">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
         <v>1.15</v>
@@ -4420,28 +4420,28 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4.65</v>
+        <v>4.99</v>
       </c>
       <c r="AA25">
         <v>1.53</v>
       </c>
       <c r="AB25">
-        <v>2.37</v>
+        <v>2.04</v>
       </c>
       <c r="AC25">
         <v>2.24</v>
       </c>
       <c r="AD25">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE25">
         <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
         <v>3.84</v>
@@ -4556,7 +4556,7 @@
         <v>1.89</v>
       </c>
       <c r="Q26">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R26">
         <v>2</v>
@@ -4571,40 +4571,40 @@
         <v>3.2</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
         <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB26">
         <v>1.65</v>
       </c>
       <c r="AC26">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AD26">
         <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG26">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
         <v>2.94</v>
@@ -4743,25 +4743,25 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
         <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
         <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
         <v>1.43</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,13 +4882,13 @@
         <v>2.07</v>
       </c>
       <c r="Q28">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="R28">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
         <v>3.6</v>
@@ -4909,28 +4909,28 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AB28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
         <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
         <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,19 +5045,19 @@
         <v>3.53</v>
       </c>
       <c r="Q29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T29">
         <v>3.32</v>
       </c>
       <c r="U29">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
         <v>1.53</v>
@@ -5069,31 +5069,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA29">
         <v>1.65</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC29">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         <v>4.75</v>
       </c>
       <c r="Q30">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U30">
         <v>2.32</v>
@@ -5226,10 +5226,10 @@
         <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.13</v>
@@ -5244,19 +5244,19 @@
         <v>2.27</v>
       </c>
       <c r="AC30">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
         <v>2.05</v>
@@ -5371,10 +5371,10 @@
         <v>3.93</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
         <v>1.21</v>
@@ -5386,10 +5386,10 @@
         <v>2.15</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5401,7 +5401,7 @@
         <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB31">
         <v>2.33</v>
@@ -5413,26 +5413,26 @@
         <v>1.57</v>
       </c>
       <c r="AE31">
+        <v>1.24</v>
+      </c>
+      <c r="AF31">
+        <v>1.65</v>
+      </c>
+      <c r="AG31">
+        <v>2.21</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.18</v>
-      </c>
-      <c r="AF31">
-        <v>1.59</v>
-      </c>
-      <c r="AG31">
-        <v>2.18</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.17</v>
       </c>
       <c r="AK31">
         <v>2.38</v>
@@ -5537,7 +5537,7 @@
         <v>1.88</v>
       </c>
       <c r="R32">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="S32">
         <v>1.2</v>
@@ -5555,34 +5555,34 @@
         <v>1.16</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC32">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD32">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
         <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>3.02</v>
+        <v>3.78</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA2">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC2">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE2">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG2">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1000,10 +1000,10 @@
         <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O7">
         <v>3.5</v>
@@ -1468,13 +1468,13 @@
         <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="U7">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
         <v>1.06</v>
@@ -1483,19 +1483,19 @@
         <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z7">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AA7">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB7">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD7">
         <v>1.22</v>
@@ -1504,10 +1504,10 @@
         <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -1634,10 +1634,10 @@
         <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1649,13 +1649,13 @@
         <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA8">
         <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
         <v>2.88</v>
@@ -1667,7 +1667,7 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
         <v>2.25</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK8">
         <v>1.33</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="O9">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="P9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="W9">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z9">
-        <v>6.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AB9">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC9">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AD9">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AE9">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="O10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>2.83</v>
+        <v>1.78</v>
       </c>
       <c r="Q10">
+        <v>3.6</v>
+      </c>
+      <c r="R10">
+        <v>2.3</v>
+      </c>
+      <c r="S10">
+        <v>1.15</v>
+      </c>
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>1.57</v>
+      </c>
+      <c r="W10">
+        <v>1.13</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.07</v>
+      </c>
+      <c r="Z10">
         <v>3.75</v>
       </c>
-      <c r="R10">
-        <v>2.41</v>
-      </c>
-      <c r="S10">
-        <v>1.2</v>
-      </c>
-      <c r="T10">
-        <v>4</v>
-      </c>
-      <c r="U10">
-        <v>2.1</v>
-      </c>
-      <c r="V10">
-        <v>1.67</v>
-      </c>
-      <c r="W10">
-        <v>1.17</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.08</v>
-      </c>
-      <c r="Z10">
-        <v>5.6</v>
-      </c>
       <c r="AA10">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB10">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AD10">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AE10">
+        <v>1.22</v>
+      </c>
+      <c r="AF10">
         <v>1.3</v>
       </c>
-      <c r="AF10">
-        <v>1.4</v>
-      </c>
       <c r="AG10">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O11">
         <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q11">
+        <v>2.2</v>
+      </c>
+      <c r="R11">
         <v>2.18</v>
-      </c>
-      <c r="R11">
-        <v>2.41</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2123,31 +2123,31 @@
         <v>2.91</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="V11">
         <v>1.47</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="AA11">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB11">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>5.45</v>
+        <v>6.1</v>
       </c>
       <c r="R13">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2449,43 +2449,43 @@
         <v>2.62</v>
       </c>
       <c r="U13">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
         <v>1.07</v>
       </c>
-      <c r="X13">
-        <v>1.06</v>
-      </c>
       <c r="Y13">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z13">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC13">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AK13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="R14">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2624,31 +2624,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,13 +2757,13 @@
         <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q15">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2775,13 +2775,13 @@
         <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
         <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2793,10 +2793,10 @@
         <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB15">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AC15">
         <v>2.7</v>
@@ -2808,10 +2808,10 @@
         <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="R16">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2959,7 +2959,7 @@
         <v>1.81</v>
       </c>
       <c r="AB16">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC16">
         <v>3.2</v>
@@ -2990,7 +2990,7 @@
         <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q17">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
         <v>3.3</v>
@@ -3107,7 +3107,7 @@
         <v>1.52</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3119,25 +3119,25 @@
         <v>4.33</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
         <v>2.11</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="O18">
         <v>3.4</v>
@@ -3255,10 +3255,10 @@
         <v>3.28</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
         <v>3.25</v>
@@ -3267,7 +3267,7 @@
         <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
         <v>1.09</v>
@@ -3285,16 +3285,16 @@
         <v>1.69</v>
       </c>
       <c r="AB18">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AC18">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD18">
         <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,31 +3409,31 @@
         <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="Q19">
         <v>2.98</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
         <v>2.5</v>
       </c>
       <c r="U19">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.06</v>
@@ -3445,25 +3445,25 @@
         <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
         <v>1.66</v>
       </c>
       <c r="AC19">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
         <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="Q20">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
         <v>1.33</v>
@@ -3590,13 +3590,13 @@
         <v>2.74</v>
       </c>
       <c r="U20">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3623,10 +3623,10 @@
         <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P21">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
         <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U21">
         <v>2.63</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC21">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
         <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,22 +3895,22 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
         <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
         <v>2.98</v>
@@ -3925,7 +3925,7 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.3</v>
@@ -3934,7 +3934,7 @@
         <v>3.4</v>
       </c>
       <c r="AA22">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AB22">
         <v>1.83</v>
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P23">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="Q23">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
         <v>1.4</v>
@@ -4097,13 +4097,13 @@
         <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="AD23">
         <v>1.25</v>
@@ -4112,10 +4112,10 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,22 +4221,22 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R24">
         <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>3.25</v>
@@ -4260,7 +4260,7 @@
         <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
         <v>2.14</v>
@@ -4278,7 +4278,7 @@
         <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.76</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4380,17 +4380,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
         <v>1.22</v>
       </c>
       <c r="O25">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4399,16 +4399,16 @@
         <v>2.71</v>
       </c>
       <c r="S25">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W25">
         <v>1.15</v>
@@ -4420,10 +4420,10 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4.99</v>
+        <v>5.05</v>
       </c>
       <c r="AA25">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB25">
         <v>2.04</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q26">
         <v>4.25</v>
@@ -4586,10 +4586,10 @@
         <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB26">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC26">
         <v>4.1</v>
@@ -4601,10 +4601,10 @@
         <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG26">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4713,28 +4713,28 @@
         <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
+        <v>2.55</v>
+      </c>
+      <c r="R27">
         <v>2.5</v>
       </c>
-      <c r="R27">
-        <v>2.4</v>
-      </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
         <v>2.12</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4752,13 +4752,13 @@
         <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
         <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE27">
         <v>1.22</v>
@@ -4885,7 +4885,7 @@
         <v>3.9</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S28">
         <v>1.26</v>
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="AA28">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
         <v>2.15</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
         <v>1.3</v>
@@ -5045,7 +5045,7 @@
         <v>3.53</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="R29">
         <v>2.3</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q30">
         <v>2.1</v>
@@ -5226,7 +5226,7 @@
         <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5235,19 +5235,19 @@
         <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA30">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD30">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE30">
         <v>1.2</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>3.9</v>
       </c>
       <c r="P31">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="Q31">
         <v>1.91</v>
@@ -5383,10 +5383,10 @@
         <v>3.65</v>
       </c>
       <c r="U31">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W31">
         <v>1.14</v>
@@ -5398,25 +5398,25 @@
         <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>4.8</v>
+        <v>5.26</v>
       </c>
       <c r="AA31">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB31">
         <v>2.33</v>
       </c>
       <c r="AC31">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AD31">
         <v>1.57</v>
       </c>
       <c r="AE31">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG31">
         <v>2.21</v>
@@ -5534,25 +5534,25 @@
         <v>4.82</v>
       </c>
       <c r="Q32">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R32">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
         <v>4</v>
       </c>
       <c r="U32">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V32">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W32">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5567,22 +5567,22 @@
         <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC32">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD32">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF32">
         <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK32">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q34">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="V34">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
+        <v>1.11</v>
+      </c>
+      <c r="Z34">
+        <v>3.3</v>
+      </c>
+      <c r="AA34">
+        <v>1.44</v>
+      </c>
+      <c r="AB34">
+        <v>1.99</v>
+      </c>
+      <c r="AC34">
+        <v>2</v>
+      </c>
+      <c r="AD34">
+        <v>1.43</v>
+      </c>
+      <c r="AE34">
+        <v>1.14</v>
+      </c>
+      <c r="AF34">
+        <v>1.36</v>
+      </c>
+      <c r="AG34">
+        <v>2.1</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.08</v>
       </c>
-      <c r="Z34">
-        <v>5.45</v>
-      </c>
-      <c r="AA34">
-        <v>1.47</v>
-      </c>
-      <c r="AB34">
-        <v>2.63</v>
-      </c>
-      <c r="AC34">
-        <v>2.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.7</v>
-      </c>
-      <c r="AE34">
-        <v>1.25</v>
-      </c>
-      <c r="AF34">
-        <v>1.44</v>
-      </c>
-      <c r="AG34">
-        <v>2.63</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.17</v>
-      </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O35">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P35">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>1.81</v>
@@ -6029,40 +6029,40 @@
         <v>2.46</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA35">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB35">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
         <v>1.17</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK35">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,58 +6177,58 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P36">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Q36">
-        <v>3.92</v>
+        <v>5.34</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA36">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
         <v>1.67</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
+        <v>1.17</v>
+      </c>
+      <c r="AK36">
         <v>1.18</v>
-      </c>
-      <c r="AK36">
-        <v>1.22</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="P37">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S37">
         <v>1.43</v>
       </c>
       <c r="T37">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="U37">
         <v>2.96</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6376,16 +6376,16 @@
         <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA37">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC37">
-        <v>3.73</v>
+        <v>4.1</v>
       </c>
       <c r="AD37">
         <v>1.22</v>
@@ -6413,7 +6413,7 @@
         <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -612,130 +612,130 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="R2">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
         <v>3</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC2">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AD2">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
         <v>2.19</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "75"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>1.78</v>
       </c>
       <c r="S3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T3">
         <v>2.19</v>
@@ -855,7 +855,7 @@
         <v>2.25</v>
       </c>
       <c r="AG3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>2.6</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
         <v>2.7</v>
@@ -1000,10 +1000,10 @@
         <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1616,7 +1616,7 @@
         <v>2.8</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
         <v>2.15</v>
@@ -1634,10 +1634,10 @@
         <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1646,31 +1646,31 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB8">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
         <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1779,16 +1779,16 @@
         <v>1.2</v>
       </c>
       <c r="O9">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q9">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="R9">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="S9">
         <v>1.11</v>
@@ -1800,10 +1800,10 @@
         <v>1.63</v>
       </c>
       <c r="V9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1815,25 +1815,25 @@
         <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AB9">
         <v>2.75</v>
       </c>
       <c r="AC9">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AD9">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.06</v>
       </c>
       <c r="AK9">
-        <v>4.5</v>
+        <v>3.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>3.8</v>
       </c>
       <c r="P10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -1972,10 +1972,10 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA10">
         <v>1.3</v>
@@ -1984,10 +1984,10 @@
         <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD10">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AE10">
         <v>1.22</v>
@@ -2105,16 +2105,16 @@
         <v>1.68</v>
       </c>
       <c r="O11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="S11">
         <v>1.3</v>
@@ -2123,7 +2123,7 @@
         <v>2.91</v>
       </c>
       <c r="U11">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
         <v>1.47</v>
@@ -2132,28 +2132,28 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="AA11">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB11">
         <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AD11">
         <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
         <v>1.67</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
         <v>3.9</v>
@@ -2775,13 +2775,13 @@
         <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2793,7 +2793,7 @@
         <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
         <v>2.21</v>
@@ -2808,7 +2808,7 @@
         <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
         <v>2.26</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
         <v>1.1</v>
@@ -2956,13 +2956,13 @@
         <v>3.6</v>
       </c>
       <c r="AA16">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD16">
         <v>1.36</v>
@@ -2990,7 +2990,7 @@
         <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
         <v>3.35</v>
       </c>
       <c r="Q17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R17">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
         <v>3.3</v>
@@ -3104,40 +3104,40 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
         <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AC17">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O18">
         <v>3.4</v>
@@ -3252,55 +3252,55 @@
         <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="R18">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
+        <v>2.3</v>
+      </c>
+      <c r="V18">
+        <v>1.57</v>
+      </c>
+      <c r="W18">
+        <v>1.11</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.13</v>
+      </c>
+      <c r="Z18">
+        <v>4.6</v>
+      </c>
+      <c r="AA18">
+        <v>1.57</v>
+      </c>
+      <c r="AB18">
+        <v>2.31</v>
+      </c>
+      <c r="AC18">
         <v>2.38</v>
       </c>
-      <c r="V18">
-        <v>1.52</v>
-      </c>
-      <c r="W18">
-        <v>1.09</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
+      <c r="AD18">
+        <v>1.46</v>
+      </c>
+      <c r="AE18">
         <v>1.2</v>
       </c>
-      <c r="Z18">
-        <v>4.33</v>
-      </c>
-      <c r="AA18">
-        <v>1.69</v>
-      </c>
-      <c r="AB18">
-        <v>2.23</v>
-      </c>
-      <c r="AC18">
-        <v>2.7</v>
-      </c>
-      <c r="AD18">
-        <v>1.4</v>
-      </c>
-      <c r="AE18">
-        <v>1.14</v>
-      </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="O19">
         <v>3.2</v>
@@ -3418,19 +3418,19 @@
         <v>2.98</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S19">
         <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U19">
         <v>3</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
         <v>1.07</v>
@@ -3445,10 +3445,10 @@
         <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB19">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC19">
         <v>3.8</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R20">
         <v>2.15</v>
@@ -3593,7 +3593,7 @@
         <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.1</v>
@@ -3608,7 +3608,7 @@
         <v>3.5</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
         <v>1.93</v>
@@ -3617,7 +3617,7 @@
         <v>2.81</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
         <v>1.09</v>
@@ -3642,7 +3642,7 @@
         <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,62 +3735,62 @@
         <v>2.08</v>
       </c>
       <c r="O21">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="P21">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
         <v>2.7</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U21">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA21">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
+        <v>1.83</v>
+      </c>
+      <c r="AC21">
+        <v>3.6</v>
+      </c>
+      <c r="AD21">
+        <v>1.3</v>
+      </c>
+      <c r="AE21">
+        <v>1.06</v>
+      </c>
+      <c r="AF21">
+        <v>1.72</v>
+      </c>
+      <c r="AG21">
         <v>1.95</v>
       </c>
-      <c r="AC21">
-        <v>3.23</v>
-      </c>
-      <c r="AD21">
-        <v>1.36</v>
-      </c>
-      <c r="AE21">
-        <v>1.1</v>
-      </c>
-      <c r="AF21">
-        <v>1.62</v>
-      </c>
-      <c r="AG21">
-        <v>2.13</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O22">
         <v>3.2</v>
@@ -3904,55 +3904,55 @@
         <v>3.35</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>4.11</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
+        <v>3.6</v>
+      </c>
+      <c r="P23">
+        <v>2.07</v>
+      </c>
+      <c r="Q23">
+        <v>4.17</v>
+      </c>
+      <c r="R23">
+        <v>2.3</v>
+      </c>
+      <c r="S23">
+        <v>1.3</v>
+      </c>
+      <c r="T23">
         <v>3.22</v>
       </c>
-      <c r="P23">
-        <v>3.64</v>
-      </c>
-      <c r="Q23">
-        <v>2.49</v>
-      </c>
-      <c r="R23">
-        <v>2.16</v>
-      </c>
-      <c r="S23">
+      <c r="U23">
+        <v>2.45</v>
+      </c>
+      <c r="V23">
+        <v>1.44</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>4.2</v>
+      </c>
+      <c r="AA23">
+        <v>1.8</v>
+      </c>
+      <c r="AB23">
+        <v>2.04</v>
+      </c>
+      <c r="AC23">
+        <v>2.88</v>
+      </c>
+      <c r="AD23">
         <v>1.4</v>
       </c>
-      <c r="T23">
-        <v>2.67</v>
-      </c>
-      <c r="U23">
-        <v>2.88</v>
-      </c>
-      <c r="V23">
-        <v>1.35</v>
-      </c>
-      <c r="W23">
-        <v>1.04</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.36</v>
-      </c>
-      <c r="Z23">
-        <v>3.1</v>
-      </c>
-      <c r="AA23">
-        <v>2.19</v>
-      </c>
-      <c r="AB23">
-        <v>1.66</v>
-      </c>
-      <c r="AC23">
-        <v>4.1</v>
-      </c>
-      <c r="AD23">
-        <v>1.25</v>
-      </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AK23">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
+        <v>3.35</v>
+      </c>
+      <c r="Q24">
+        <v>2.7</v>
+      </c>
+      <c r="R24">
+        <v>2.25</v>
+      </c>
+      <c r="S24">
+        <v>1.36</v>
+      </c>
+      <c r="T24">
+        <v>2.98</v>
+      </c>
+      <c r="U24">
+        <v>2.88</v>
+      </c>
+      <c r="V24">
+        <v>1.36</v>
+      </c>
+      <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.3</v>
+      </c>
+      <c r="Z24">
+        <v>3.4</v>
+      </c>
+      <c r="AA24">
+        <v>2.01</v>
+      </c>
+      <c r="AB24">
+        <v>1.83</v>
+      </c>
+      <c r="AC24">
+        <v>3.4</v>
+      </c>
+      <c r="AD24">
+        <v>1.3</v>
+      </c>
+      <c r="AE24">
+        <v>1.1</v>
+      </c>
+      <c r="AF24">
+        <v>1.73</v>
+      </c>
+      <c r="AG24">
         <v>2</v>
       </c>
-      <c r="Q24">
-        <v>4.05</v>
-      </c>
-      <c r="R24">
-        <v>2.3</v>
-      </c>
-      <c r="S24">
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.3</v>
       </c>
-      <c r="T24">
-        <v>3.25</v>
-      </c>
-      <c r="U24">
-        <v>2.45</v>
-      </c>
-      <c r="V24">
-        <v>1.44</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4.33</v>
-      </c>
-      <c r="AA24">
-        <v>1.73</v>
-      </c>
-      <c r="AB24">
-        <v>2.14</v>
-      </c>
-      <c r="AC24">
-        <v>2.88</v>
-      </c>
-      <c r="AD24">
-        <v>1.4</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
-      <c r="AF24">
-        <v>1.6</v>
-      </c>
-      <c r="AG24">
-        <v>2.45</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.76</v>
-      </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O26">
         <v>3.15</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q26">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="R26">
         <v>2</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U26">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA26">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
         <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
         <v>2.55</v>
@@ -4728,7 +4728,7 @@
         <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
         <v>2.12</v>
@@ -4882,22 +4882,22 @@
         <v>2.07</v>
       </c>
       <c r="Q28">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R28">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
         <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V28">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W28">
         <v>1.11</v>
@@ -4909,28 +4909,28 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.27</v>
+        <v>4.76</v>
       </c>
       <c r="AA28">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC28">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
         <v>1.3</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
         <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T29">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>4</v>
+        <v>4.64</v>
       </c>
       <c r="AA29">
+        <v>1.61</v>
+      </c>
+      <c r="AB29">
+        <v>2.25</v>
+      </c>
+      <c r="AC29">
+        <v>2.61</v>
+      </c>
+      <c r="AD29">
+        <v>1.49</v>
+      </c>
+      <c r="AE29">
+        <v>1.2</v>
+      </c>
+      <c r="AF29">
         <v>1.65</v>
       </c>
-      <c r="AB29">
-        <v>2.15</v>
-      </c>
-      <c r="AC29">
-        <v>2.63</v>
-      </c>
-      <c r="AD29">
-        <v>1.41</v>
-      </c>
-      <c r="AE29">
-        <v>1.14</v>
-      </c>
-      <c r="AF29">
-        <v>1.56</v>
-      </c>
       <c r="AG29">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P30">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S30">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="T30">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V30">
+        <v>1.62</v>
+      </c>
+      <c r="W30">
+        <v>1.14</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.12</v>
+      </c>
+      <c r="Z30">
+        <v>5.27</v>
+      </c>
+      <c r="AA30">
         <v>1.52</v>
       </c>
-      <c r="W30">
-        <v>1.09</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.13</v>
-      </c>
-      <c r="Z30">
-        <v>4.75</v>
-      </c>
-      <c r="AA30">
-        <v>1.6</v>
-      </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC30">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AD30">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF30">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG30">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>4.1</v>
+        <v>4.82</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.26</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AC31">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AD31">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE31">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF31">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK31">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="P32">
-        <v>4.82</v>
+        <v>3.53</v>
       </c>
       <c r="Q32">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R32">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="U32">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AD32">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
         <v>1.2</v>
       </c>
       <c r="T33">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z33">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB33">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AC33">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD33">
+        <v>1.43</v>
+      </c>
+      <c r="AE33">
+        <v>1.14</v>
+      </c>
+      <c r="AF33">
         <v>1.36</v>
       </c>
-      <c r="AE33">
-        <v>1.11</v>
-      </c>
-      <c r="AF33">
-        <v>1.4</v>
-      </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.2</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
+        <v>1.13</v>
+      </c>
+      <c r="Z34">
+        <v>3.13</v>
+      </c>
+      <c r="AA34">
+        <v>1.49</v>
+      </c>
+      <c r="AB34">
+        <v>1.89</v>
+      </c>
+      <c r="AC34">
+        <v>2.15</v>
+      </c>
+      <c r="AD34">
+        <v>1.36</v>
+      </c>
+      <c r="AE34">
         <v>1.11</v>
       </c>
-      <c r="Z34">
-        <v>3.3</v>
-      </c>
-      <c r="AA34">
-        <v>1.44</v>
-      </c>
-      <c r="AB34">
-        <v>1.99</v>
-      </c>
-      <c r="AC34">
-        <v>2</v>
-      </c>
-      <c r="AD34">
-        <v>1.43</v>
-      </c>
-      <c r="AE34">
-        <v>1.14</v>
-      </c>
       <c r="AF34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "58", "90"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>2.6</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
         <v>2.7</v>
@@ -1000,10 +1000,10 @@
         <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q5">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R5">
         <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V5">
         <v>1.4</v>
@@ -1154,34 +1154,34 @@
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC5">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>6.29</v>
+        <v>6.42</v>
       </c>
       <c r="R6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S6">
         <v>1.55</v>
@@ -1329,13 +1329,13 @@
         <v>2.74</v>
       </c>
       <c r="AB6">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC6">
         <v>3.9</v>
       </c>
       <c r="AD6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -1468,28 +1468,28 @@
         <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="V7">
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA7">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB7">
         <v>1.66</v>
@@ -1501,13 +1501,13 @@
         <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.33</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="O9">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q9">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T9">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="V9">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z9">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="AA9">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AB9">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD9">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AE9">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AF9">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK9">
-        <v>3.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.65</v>
+        <v>1.2</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="P10">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z10">
-        <v>5.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AB10">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD10">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AF10">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>3.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,43 +2102,43 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P11">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="R11">
         <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
         <v>2.91</v>
       </c>
       <c r="U11">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z11">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="AA11">
         <v>1.74</v>
@@ -2147,19 +2147,19 @@
         <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK11">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2286,34 +2286,34 @@
         <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,43 +2437,43 @@
         <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>6.1</v>
+        <v>6.53</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
         <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z13">
         <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="AD13">
         <v>1.2</v>
@@ -2482,10 +2482,10 @@
         <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG13">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
         <v>2.29</v>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U14">
         <v>2.4</v>
@@ -2618,37 +2618,37 @@
         <v>1.59</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA14">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB14">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC14">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O15">
         <v>3.9</v>
@@ -2763,34 +2763,34 @@
         <v>4.1</v>
       </c>
       <c r="Q15">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="V15">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA15">
         <v>1.66</v>
@@ -2799,19 +2799,19 @@
         <v>2.21</v>
       </c>
       <c r="AC15">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
         <v>2.98</v>
@@ -2932,49 +2932,49 @@
         <v>2.11</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
         <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
         <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK16">
         <v>1.37</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="Q17">
         <v>2.34</v>
@@ -3116,7 +3116,7 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="AA17">
         <v>1.69</v>
@@ -3134,10 +3134,10 @@
         <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
         <v>3.4</v>
@@ -3255,7 +3255,7 @@
         <v>3.31</v>
       </c>
       <c r="R18">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3267,7 +3267,7 @@
         <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
         <v>1.11</v>
@@ -3294,7 +3294,7 @@
         <v>1.46</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
         <v>1.53</v>
@@ -3415,16 +3415,16 @@
         <v>2.81</v>
       </c>
       <c r="Q19">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="R19">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="U19">
         <v>3</v>
@@ -3445,22 +3445,22 @@
         <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AB19">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AC19">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
         <v>1.91</v>
@@ -3479,7 +3479,7 @@
         <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>2.74</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -3611,7 +3611,7 @@
         <v>1.93</v>
       </c>
       <c r="AB20">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
         <v>2.81</v>
@@ -3741,7 +3741,7 @@
         <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
         <v>2.1</v>
@@ -3762,25 +3762,25 @@
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB21">
         <v>1.83</v>
       </c>
       <c r="AC21">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
@@ -3789,7 +3789,7 @@
         <v>1.72</v>
       </c>
       <c r="AG21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,16 +3898,16 @@
         <v>2.06</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>2.54</v>
       </c>
       <c r="R22">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
         <v>1.4</v>
@@ -3940,10 +3940,10 @@
         <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>4.11</v>
+        <v>4.01</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -4115,7 +4115,7 @@
         <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.77</v>
       </c>
       <c r="AK23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O24">
         <v>3.35</v>
       </c>
       <c r="P24">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <v>2.7</v>
@@ -4278,7 +4278,7 @@
         <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q26">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S26">
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U26">
         <v>3</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4589,7 +4589,7 @@
         <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
         <v>3.8</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6014,43 +6014,43 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="O35">
         <v>5.5</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q35">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R35">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
         <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA35">
         <v>1.64</v>
@@ -6062,7 +6062,7 @@
         <v>2.6</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE35">
         <v>1.17</v>
@@ -6071,7 +6071,7 @@
         <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK35">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,61 +6180,61 @@
         <v>4.5</v>
       </c>
       <c r="O36">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Q36">
-        <v>5.34</v>
+        <v>4.83</v>
       </c>
       <c r="R36">
         <v>2.31</v>
       </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="V36">
         <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC36">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE36">
         <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O37">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="U37">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W37">
         <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA37">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB37">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC37">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD37">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "62"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "26"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
         <v>3.8</v>
       </c>
       <c r="P9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R9">
         <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9">
         <v>2</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,19 +1812,19 @@
         <v>1.08</v>
       </c>
       <c r="Z9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC9">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD9">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE9">
         <v>1.22</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,28 +1948,28 @@
         <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="R10">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U10">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V10">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10">
         <v>1.03</v>
@@ -1978,25 +1978,25 @@
         <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AB10">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AC10">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD10">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AE10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AF10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK10">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,40 +2105,40 @@
         <v>1.58</v>
       </c>
       <c r="O11">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="Q11">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="R11">
         <v>2.24</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
         <v>2.91</v>
       </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AA11">
         <v>1.74</v>
@@ -2147,19 +2147,19 @@
         <v>2.06</v>
       </c>
       <c r="AC11">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
         <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>2.45</v>
       </c>
       <c r="O12">
+        <v>3.15</v>
+      </c>
+      <c r="P12">
+        <v>2.5</v>
+      </c>
+      <c r="Q12">
+        <v>3.1</v>
+      </c>
+      <c r="R12">
+        <v>2.05</v>
+      </c>
+      <c r="S12">
+        <v>1.36</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
+        <v>2.73</v>
+      </c>
+      <c r="V12">
+        <v>1.38</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.04</v>
+      </c>
+      <c r="Y12">
+        <v>1.3</v>
+      </c>
+      <c r="Z12">
         <v>3.2</v>
       </c>
-      <c r="P12">
-        <v>2.65</v>
-      </c>
-      <c r="Q12">
-        <v>3.04</v>
-      </c>
-      <c r="R12">
-        <v>2.06</v>
-      </c>
-      <c r="S12">
-        <v>1.35</v>
-      </c>
-      <c r="T12">
-        <v>2.9</v>
-      </c>
-      <c r="U12">
-        <v>2.62</v>
-      </c>
-      <c r="V12">
-        <v>1.41</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.29</v>
-      </c>
-      <c r="Z12">
-        <v>3.3</v>
-      </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC12">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>6.53</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
+        <v>1.51</v>
+      </c>
+      <c r="T13">
+        <v>2.33</v>
+      </c>
+      <c r="U13">
+        <v>3.2</v>
+      </c>
+      <c r="V13">
+        <v>1.29</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.05</v>
+      </c>
+      <c r="Y13">
         <v>1.44</v>
       </c>
-      <c r="T13">
-        <v>2.5</v>
-      </c>
-      <c r="U13">
-        <v>3.08</v>
-      </c>
-      <c r="V13">
-        <v>1.31</v>
-      </c>
-      <c r="W13">
-        <v>1.04</v>
-      </c>
-      <c r="X13">
-        <v>1.07</v>
-      </c>
-      <c r="Y13">
-        <v>1.4</v>
-      </c>
       <c r="Z13">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA13">
         <v>2.4</v>
@@ -2473,19 +2473,19 @@
         <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="AD13">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AG13">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="O14">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="R14">
         <v>2.29</v>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.4</v>
@@ -2618,10 +2618,10 @@
         <v>1.59</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.17</v>
@@ -2630,22 +2630,22 @@
         <v>4.25</v>
       </c>
       <c r="AA14">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
         <v>2.3</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="O15">
         <v>3.9</v>
@@ -2763,7 +2763,7 @@
         <v>4.1</v>
       </c>
       <c r="Q15">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R15">
         <v>2.4</v>
@@ -2772,13 +2772,13 @@
         <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="U15">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2799,13 +2799,13 @@
         <v>2.21</v>
       </c>
       <c r="AC15">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
         <v>1.62</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
         <v>2.98</v>
@@ -2938,7 +2938,7 @@
         <v>3.19</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
         <v>1.44</v>
@@ -2947,19 +2947,19 @@
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
         <v>2.75</v>
@@ -2971,7 +2971,7 @@
         <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
         <v>2.2</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
         <v>1.37</v>
@@ -3083,10 +3083,10 @@
         <v>2</v>
       </c>
       <c r="O17">
+        <v>3.5</v>
+      </c>
+      <c r="P17">
         <v>3.4</v>
-      </c>
-      <c r="P17">
-        <v>2.88</v>
       </c>
       <c r="Q17">
         <v>2.34</v>
@@ -3116,7 +3116,7 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="AA17">
         <v>1.69</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>1.85</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
         <v>3.31</v>
       </c>
       <c r="R18">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
         <v>1.25</v>
@@ -3264,34 +3264,34 @@
         <v>3.4</v>
       </c>
       <c r="U18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
         <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB18">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD18">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE18">
         <v>1.21</v>
@@ -3415,13 +3415,13 @@
         <v>2.81</v>
       </c>
       <c r="Q19">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T19">
         <v>2.76</v>
@@ -3445,10 +3445,10 @@
         <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB19">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
         <v>3.5</v>
@@ -3460,10 +3460,10 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>2.14</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
         <v>3.2</v>
@@ -3590,7 +3590,7 @@
         <v>2.74</v>
       </c>
       <c r="U20">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
         <v>3.28</v>
@@ -3750,7 +3750,7 @@
         <v>1.41</v>
       </c>
       <c r="T21">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
         <v>2.78</v>
@@ -3777,7 +3777,7 @@
         <v>1.83</v>
       </c>
       <c r="AC21">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="AD21">
         <v>1.29</v>
@@ -3901,13 +3901,13 @@
         <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q22">
         <v>2.54</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
         <v>1.4</v>
@@ -3940,10 +3940,10 @@
         <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="O23">
         <v>3.6</v>
@@ -4067,7 +4067,7 @@
         <v>2.07</v>
       </c>
       <c r="Q23">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="R23">
         <v>2.3</v>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="U23">
         <v>2.45</v>
@@ -4115,7 +4115,7 @@
         <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.77</v>
       </c>
       <c r="AK23">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,37 +4221,37 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
         <v>3.35</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q24">
         <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="U24">
         <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
         <v>1.05</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.3</v>
@@ -4278,7 +4278,7 @@
         <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK24">
         <v>1.65</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O25">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="P25">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4402,16 +4402,16 @@
         <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4420,13 +4420,13 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA25">
         <v>1.48</v>
       </c>
       <c r="AB25">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AC25">
         <v>2.24</v>
@@ -4719,25 +4719,25 @@
         <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="R27">
         <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U27">
         <v>2.12</v>
       </c>
       <c r="V27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4752,7 +4752,7 @@
         <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC27">
         <v>2.3</v>
@@ -4909,13 +4909,13 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="AA28">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC28">
         <v>2.41</v>
@@ -4930,7 +4930,7 @@
         <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>3.53</v>
       </c>
       <c r="Q29">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R29">
         <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="U29">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>4.64</v>
+        <v>3.8</v>
       </c>
       <c r="AA29">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AB29">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC29">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>1.8</v>
       </c>
       <c r="O30">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P30">
         <v>4.1</v>
@@ -5214,49 +5214,49 @@
         <v>2.5</v>
       </c>
       <c r="S30">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T30">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="U30">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V30">
         <v>1.62</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
-        <v>5.27</v>
+        <v>4.9</v>
       </c>
       <c r="AA30">
         <v>1.52</v>
       </c>
       <c r="AB30">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC30">
         <v>2.33</v>
       </c>
       <c r="AD30">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE30">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
         <v>2.38</v>
@@ -5383,13 +5383,13 @@
         <v>4</v>
       </c>
       <c r="U31">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
         <v>1.67</v>
       </c>
       <c r="W31">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5404,22 +5404,22 @@
         <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC31">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE31">
         <v>1.29</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O32">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>3.53</v>
+        <v>4.8</v>
       </c>
       <c r="Q32">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
         <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T32">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>3.8</v>
+        <v>4.64</v>
       </c>
       <c r="AA32">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5700,7 +5700,7 @@
         <v>2.2</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
         <v>1.2</v>
@@ -5709,43 +5709,43 @@
         <v>2.75</v>
       </c>
       <c r="U33">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD33">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="O34">
         <v>3.6</v>
@@ -5860,55 +5860,55 @@
         <v>3.55</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
+        <v>1.11</v>
+      </c>
+      <c r="Z34">
+        <v>3.3</v>
+      </c>
+      <c r="AA34">
+        <v>1.58</v>
+      </c>
+      <c r="AB34">
+        <v>2.29</v>
+      </c>
+      <c r="AC34">
+        <v>2.35</v>
+      </c>
+      <c r="AD34">
+        <v>1.47</v>
+      </c>
+      <c r="AE34">
         <v>1.13</v>
       </c>
-      <c r="Z34">
-        <v>3.13</v>
-      </c>
-      <c r="AA34">
-        <v>1.49</v>
-      </c>
-      <c r="AB34">
-        <v>1.89</v>
-      </c>
-      <c r="AC34">
-        <v>2.15</v>
-      </c>
-      <c r="AD34">
-        <v>1.36</v>
-      </c>
-      <c r="AE34">
-        <v>1.11</v>
-      </c>
       <c r="AF34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="O35">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P35">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Q35">
         <v>1.76</v>
       </c>
       <c r="R35">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>4.45</v>
+        <v>3.86</v>
       </c>
       <c r="AA35">
         <v>1.64</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG35">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,31 +6183,31 @@
         <v>3.7</v>
       </c>
       <c r="P36">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q36">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="R36">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W36">
         <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.17</v>
@@ -6216,19 +6216,19 @@
         <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB36">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC36">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AD36">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
         <v>1.62</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>2.05</v>
       </c>
       <c r="O37">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
         <v>2.7</v>
@@ -6361,10 +6361,10 @@
         <v>2.7</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="V37">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6385,13 +6385,13 @@
         <v>1.82</v>
       </c>
       <c r="AC37">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="AD37">
         <v>1.3</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
         <v>1.73</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
         <v>1.71</v>

--- a/jogos_2026-10-27.xlsx
+++ b/jogos_2026-10-27.xlsx
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1756,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "73"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "85"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2254,14 +2254,14 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "72", "82"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85", "88"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,11 +2420,11 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,26 +2568,26 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "43"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "13", "16", "45+1", "55", "65"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3069,14 +3069,14 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "85"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "90"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O25">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="Q25">
         <v>1.6</v>
@@ -4420,13 +4420,13 @@
         <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="AA25">
         <v>1.48</v>
       </c>
       <c r="AB25">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AC25">
         <v>2.24</v>
@@ -4438,7 +4438,7 @@
         <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
         <v>1.68</v>
@@ -4752,7 +4752,7 @@
         <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
         <v>2.3</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.09</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>2.07</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="V28">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
+        <v>1.15</v>
+      </c>
+      <c r="Z28">
+        <v>4.27</v>
+      </c>
+      <c r="AA28">
+        <v>1.7</v>
+      </c>
+      <c r="AB28">
+        <v>2.1</v>
+      </c>
+      <c r="AC28">
+        <v>2.88</v>
+      </c>
+      <c r="AD28">
+        <v>1.44</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.8</v>
+      </c>
+      <c r="AG28">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.2</v>
       </c>
-      <c r="Z28">
-        <v>4.73</v>
-      </c>
-      <c r="AA28">
-        <v>1.65</v>
-      </c>
-      <c r="AB28">
-        <v>2.27</v>
-      </c>
-      <c r="AC28">
-        <v>2.41</v>
-      </c>
-      <c r="AD28">
-        <v>1.45</v>
-      </c>
-      <c r="AE28">
-        <v>1.17</v>
-      </c>
-      <c r="AF28">
-        <v>1.5</v>
-      </c>
-      <c r="AG28">
-        <v>2.38</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.17</v>
-      </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="O29">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="P29">
-        <v>3.53</v>
+        <v>4.1</v>
       </c>
       <c r="Q29">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AB29">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="AC29">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="O30">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q30">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="R30">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="S30">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="AA30">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AB30">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AC30">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AD30">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5380,10 +5380,10 @@
         <v>1.22</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V31">
         <v>1.67</v>
@@ -5401,7 +5401,7 @@
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB31">
         <v>2.39</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P32">
-        <v>4.8</v>
+        <v>3.53</v>
       </c>
       <c r="Q32">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R32">
         <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="U32">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>4.64</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC32">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD32">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q33">
+        <v>2.05</v>
+      </c>
+      <c r="R33">
         <v>2.2</v>
       </c>
-      <c r="R33">
-        <v>2.15</v>
-      </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
+        <v>1.58</v>
+      </c>
+      <c r="AB33">
+        <v>2.29</v>
+      </c>
+      <c r="AC33">
+        <v>2.35</v>
+      </c>
+      <c r="AD33">
         <v>1.47</v>
-      </c>
-      <c r="AB33">
-        <v>2.25</v>
-      </c>
-      <c r="AC33">
-        <v>2.06</v>
-      </c>
-      <c r="AD33">
-        <v>1.4</v>
       </c>
       <c r="AE33">
         <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q34">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
+        <v>2.34</v>
+      </c>
+      <c r="V34">
+        <v>1.51</v>
+      </c>
+      <c r="W34">
+        <v>1.08</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.13</v>
+      </c>
+      <c r="Z34">
+        <v>3.2</v>
+      </c>
+      <c r="AA34">
+        <v>1.47</v>
+      </c>
+      <c r="AB34">
         <v>2.25</v>
       </c>
-      <c r="V34">
-        <v>1.57</v>
-      </c>
-      <c r="W34">
-        <v>1.09</v>
-      </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.11</v>
-      </c>
-      <c r="Z34">
-        <v>3.3</v>
-      </c>
-      <c r="AA34">
-        <v>1.58</v>
-      </c>
-      <c r="AB34">
-        <v>2.29</v>
-      </c>
       <c r="AC34">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
         <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
